--- a/php/plantilla.xlsx
+++ b/php/plantilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QLTrades\OneDrive\Documentos\2do DAW\Proyecto-Calidad\php\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A6A84E-9B36-4FF2-B3FE-0AE5BAD9A4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBB74C5-FF78-45F8-8CF4-5A370772EFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="1" r:id="rId1"/>
@@ -377,7 +377,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="165">
   <si>
     <t>PC03.F01 Acta d'avaluació Ed.02 - Setem.25</t>
   </si>
@@ -578,9 +578,6 @@
   </si>
   <si>
     <t>Observacions - Seguiment individual - Mesures d'inclusió - Pla recuperació Convalidacions - Exempcions</t>
-  </si>
-  <si>
-    <t>Sí</t>
   </si>
   <si>
     <t>No</t>
@@ -5267,12 +5264,12 @@
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
       <c r="I1" s="176" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
       <c r="L1" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M1" s="30"/>
     </row>
@@ -5373,7 +5370,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="292"/>
       <c r="K7" s="306"/>
@@ -5383,7 +5380,7 @@
     <row r="8" spans="2:25"/>
     <row r="9" spans="2:25" s="37" customFormat="1" ht="21">
       <c r="B9" s="199" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="199"/>
       <c r="D9" s="199"/>
@@ -5401,7 +5398,7 @@
     <row r="10" spans="2:25"/>
     <row r="11" spans="2:25" ht="15.6" customHeight="1">
       <c r="B11" s="269" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="269"/>
       <c r="D11" s="269"/>
@@ -5445,7 +5442,7 @@
     <row r="13" spans="2:25"/>
     <row r="14" spans="2:25">
       <c r="B14" s="269" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="269"/>
       <c r="D14" s="269"/>
@@ -5489,7 +5486,7 @@
     <row r="16" spans="2:25" ht="0" hidden="1" customHeight="1"/>
     <row r="17" spans="1:14">
       <c r="B17" s="177" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" s="177"/>
       <c r="D17" s="177"/>
@@ -5522,7 +5519,7 @@
     <row r="19" spans="1:14"/>
     <row r="20" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B20" s="199" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="199"/>
       <c r="D20" s="199"/>
@@ -5571,7 +5568,7 @@
     <row r="24" spans="1:14"/>
     <row r="25" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B25" s="199" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C25" s="199"/>
       <c r="D25" s="199"/>
@@ -5595,10 +5592,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="179" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="267" t="s">
         <v>149</v>
-      </c>
-      <c r="E27" s="267" t="s">
-        <v>150</v>
       </c>
       <c r="F27" s="267"/>
       <c r="G27" s="267"/>
@@ -5623,10 +5620,10 @@
         <v/>
       </c>
       <c r="D28" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="368" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F28" s="369"/>
       <c r="G28" s="369"/>
@@ -5651,7 +5648,7 @@
         <v/>
       </c>
       <c r="D29" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" s="365"/>
       <c r="F29" s="366"/>
@@ -5677,7 +5674,7 @@
         <v/>
       </c>
       <c r="D30" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="365"/>
       <c r="F30" s="366"/>
@@ -5703,7 +5700,7 @@
         <v/>
       </c>
       <c r="D31" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="365"/>
       <c r="F31" s="366"/>
@@ -5729,7 +5726,7 @@
         <v/>
       </c>
       <c r="D32" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E32" s="365"/>
       <c r="F32" s="366"/>
@@ -5755,7 +5752,7 @@
         <v/>
       </c>
       <c r="D33" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="365"/>
       <c r="F33" s="366"/>
@@ -5781,7 +5778,7 @@
         <v/>
       </c>
       <c r="D34" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="365"/>
       <c r="F34" s="366"/>
@@ -5807,7 +5804,7 @@
         <v/>
       </c>
       <c r="D35" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="365"/>
       <c r="F35" s="366"/>
@@ -5833,7 +5830,7 @@
         <v/>
       </c>
       <c r="D36" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="365"/>
       <c r="F36" s="366"/>
@@ -5859,7 +5856,7 @@
         <v/>
       </c>
       <c r="D37" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="365"/>
       <c r="F37" s="366"/>
@@ -5885,7 +5882,7 @@
         <v/>
       </c>
       <c r="D38" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="365"/>
       <c r="F38" s="366"/>
@@ -5911,7 +5908,7 @@
         <v/>
       </c>
       <c r="D39" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="365"/>
       <c r="F39" s="366"/>
@@ -5937,7 +5934,7 @@
         <v/>
       </c>
       <c r="D40" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="365"/>
       <c r="F40" s="366"/>
@@ -5963,7 +5960,7 @@
         <v/>
       </c>
       <c r="D41" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="365"/>
       <c r="F41" s="366"/>
@@ -5989,7 +5986,7 @@
         <v/>
       </c>
       <c r="D42" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="365"/>
       <c r="F42" s="366"/>
@@ -6015,7 +6012,7 @@
         <v/>
       </c>
       <c r="D43" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="365"/>
       <c r="F43" s="366"/>
@@ -6041,7 +6038,7 @@
         <v/>
       </c>
       <c r="D44" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="365"/>
       <c r="F44" s="366"/>
@@ -6067,7 +6064,7 @@
         <v/>
       </c>
       <c r="D45" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="365"/>
       <c r="F45" s="366"/>
@@ -6093,7 +6090,7 @@
         <v/>
       </c>
       <c r="D46" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="365"/>
       <c r="F46" s="366"/>
@@ -6119,7 +6116,7 @@
         <v/>
       </c>
       <c r="D47" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="365"/>
       <c r="F47" s="366"/>
@@ -6145,7 +6142,7 @@
         <v/>
       </c>
       <c r="D48" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="365"/>
       <c r="F48" s="366"/>
@@ -6171,7 +6168,7 @@
         <v/>
       </c>
       <c r="D49" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="365"/>
       <c r="F49" s="366"/>
@@ -6197,7 +6194,7 @@
         <v/>
       </c>
       <c r="D50" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="365"/>
       <c r="F50" s="366"/>
@@ -6223,7 +6220,7 @@
         <v/>
       </c>
       <c r="D51" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="365"/>
       <c r="F51" s="366"/>
@@ -6249,7 +6246,7 @@
         <v/>
       </c>
       <c r="D52" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="365"/>
       <c r="F52" s="366"/>
@@ -6275,7 +6272,7 @@
         <v/>
       </c>
       <c r="D53" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="365"/>
       <c r="F53" s="366"/>
@@ -6301,7 +6298,7 @@
         <v/>
       </c>
       <c r="D54" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="365"/>
       <c r="F54" s="366"/>
@@ -6327,7 +6324,7 @@
         <v/>
       </c>
       <c r="D55" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="365"/>
       <c r="F55" s="366"/>
@@ -6353,7 +6350,7 @@
         <v/>
       </c>
       <c r="D56" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="365"/>
       <c r="F56" s="366"/>
@@ -6379,7 +6376,7 @@
         <v/>
       </c>
       <c r="D57" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="365"/>
       <c r="F57" s="366"/>
@@ -6405,7 +6402,7 @@
         <v/>
       </c>
       <c r="D58" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="180"/>
       <c r="F58" s="181"/>
@@ -6431,7 +6428,7 @@
         <v/>
       </c>
       <c r="D59" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="180"/>
       <c r="F59" s="181"/>
@@ -6457,7 +6454,7 @@
         <v/>
       </c>
       <c r="D60" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="180"/>
       <c r="F60" s="181"/>
@@ -6483,7 +6480,7 @@
         <v/>
       </c>
       <c r="D61" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="180"/>
       <c r="F61" s="181"/>
@@ -6509,7 +6506,7 @@
         <v/>
       </c>
       <c r="D62" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="180"/>
       <c r="F62" s="181"/>
@@ -6535,7 +6532,7 @@
         <v/>
       </c>
       <c r="D63" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="365"/>
       <c r="F63" s="366"/>
@@ -6561,7 +6558,7 @@
         <v/>
       </c>
       <c r="D64" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="365"/>
       <c r="F64" s="366"/>
@@ -6587,7 +6584,7 @@
         <v/>
       </c>
       <c r="D65" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="365"/>
       <c r="F65" s="366"/>
@@ -6613,7 +6610,7 @@
         <v/>
       </c>
       <c r="D66" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="365"/>
       <c r="F66" s="366"/>
@@ -6639,7 +6636,7 @@
         <v/>
       </c>
       <c r="D67" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="365"/>
       <c r="F67" s="366"/>
@@ -6655,7 +6652,7 @@
     <row r="68" spans="1:14" ht="19.5" customHeight="1" thickBot="1"/>
     <row r="69" spans="1:14" s="37" customFormat="1" ht="54.75" customHeight="1" thickBot="1">
       <c r="B69" s="362" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C69" s="363"/>
       <c r="D69" s="363"/>
@@ -6698,7 +6695,7 @@
       <c r="H71" s="242"/>
       <c r="I71" s="242"/>
       <c r="J71" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K71" s="252"/>
       <c r="L71" s="252"/>
@@ -6815,7 +6812,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="244"/>
       <c r="D78" s="244"/>
@@ -6955,12 +6952,12 @@
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
       <c r="I1" s="176" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
       <c r="L1" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M1" s="30"/>
     </row>
@@ -7061,7 +7058,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="292"/>
       <c r="K7" s="306"/>
@@ -7071,7 +7068,7 @@
     <row r="8" spans="2:25"/>
     <row r="9" spans="2:25" s="37" customFormat="1" ht="21">
       <c r="B9" s="199" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="199"/>
       <c r="D9" s="199"/>
@@ -7089,7 +7086,7 @@
     <row r="10" spans="2:25"/>
     <row r="11" spans="2:25" ht="15.6" customHeight="1">
       <c r="B11" s="269" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="269"/>
       <c r="D11" s="269"/>
@@ -7133,7 +7130,7 @@
     <row r="13" spans="2:25"/>
     <row r="14" spans="2:25">
       <c r="B14" s="269" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="269"/>
       <c r="D14" s="269"/>
@@ -7177,7 +7174,7 @@
     <row r="16" spans="2:25" ht="0" hidden="1" customHeight="1"/>
     <row r="17" spans="1:14">
       <c r="B17" s="177" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" s="177"/>
       <c r="D17" s="177"/>
@@ -7210,7 +7207,7 @@
     <row r="19" spans="1:14"/>
     <row r="20" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B20" s="199" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="199"/>
       <c r="D20" s="199"/>
@@ -7259,7 +7256,7 @@
     <row r="24" spans="1:14"/>
     <row r="25" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B25" s="199" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C25" s="199"/>
       <c r="D25" s="199"/>
@@ -7283,10 +7280,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="179" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E27" s="267" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F27" s="267"/>
       <c r="G27" s="267"/>
@@ -7311,10 +7308,10 @@
         <v/>
       </c>
       <c r="D28" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="368" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F28" s="369"/>
       <c r="G28" s="369"/>
@@ -7339,7 +7336,7 @@
         <v/>
       </c>
       <c r="D29" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" s="365"/>
       <c r="F29" s="366"/>
@@ -7365,7 +7362,7 @@
         <v/>
       </c>
       <c r="D30" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="365"/>
       <c r="F30" s="366"/>
@@ -7391,7 +7388,7 @@
         <v/>
       </c>
       <c r="D31" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="365"/>
       <c r="F31" s="366"/>
@@ -7417,7 +7414,7 @@
         <v/>
       </c>
       <c r="D32" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E32" s="365"/>
       <c r="F32" s="366"/>
@@ -7443,7 +7440,7 @@
         <v/>
       </c>
       <c r="D33" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="365"/>
       <c r="F33" s="366"/>
@@ -7469,7 +7466,7 @@
         <v/>
       </c>
       <c r="D34" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="365"/>
       <c r="F34" s="366"/>
@@ -7495,7 +7492,7 @@
         <v/>
       </c>
       <c r="D35" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="365"/>
       <c r="F35" s="366"/>
@@ -7521,7 +7518,7 @@
         <v/>
       </c>
       <c r="D36" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="365"/>
       <c r="F36" s="366"/>
@@ -7547,7 +7544,7 @@
         <v/>
       </c>
       <c r="D37" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="365"/>
       <c r="F37" s="366"/>
@@ -7573,7 +7570,7 @@
         <v/>
       </c>
       <c r="D38" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="365"/>
       <c r="F38" s="366"/>
@@ -7599,7 +7596,7 @@
         <v/>
       </c>
       <c r="D39" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="365"/>
       <c r="F39" s="366"/>
@@ -7625,7 +7622,7 @@
         <v/>
       </c>
       <c r="D40" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="365"/>
       <c r="F40" s="366"/>
@@ -7651,7 +7648,7 @@
         <v/>
       </c>
       <c r="D41" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="365"/>
       <c r="F41" s="366"/>
@@ -7677,7 +7674,7 @@
         <v/>
       </c>
       <c r="D42" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="365"/>
       <c r="F42" s="366"/>
@@ -7703,7 +7700,7 @@
         <v/>
       </c>
       <c r="D43" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="365"/>
       <c r="F43" s="366"/>
@@ -7729,7 +7726,7 @@
         <v/>
       </c>
       <c r="D44" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="365"/>
       <c r="F44" s="366"/>
@@ -7755,7 +7752,7 @@
         <v/>
       </c>
       <c r="D45" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="365"/>
       <c r="F45" s="366"/>
@@ -7781,7 +7778,7 @@
         <v/>
       </c>
       <c r="D46" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="365"/>
       <c r="F46" s="366"/>
@@ -7807,7 +7804,7 @@
         <v/>
       </c>
       <c r="D47" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="365"/>
       <c r="F47" s="366"/>
@@ -7833,7 +7830,7 @@
         <v/>
       </c>
       <c r="D48" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="365"/>
       <c r="F48" s="366"/>
@@ -7859,7 +7856,7 @@
         <v/>
       </c>
       <c r="D49" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="365"/>
       <c r="F49" s="366"/>
@@ -7885,7 +7882,7 @@
         <v/>
       </c>
       <c r="D50" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="365"/>
       <c r="F50" s="366"/>
@@ -7911,7 +7908,7 @@
         <v/>
       </c>
       <c r="D51" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="365"/>
       <c r="F51" s="366"/>
@@ -7937,7 +7934,7 @@
         <v/>
       </c>
       <c r="D52" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="365"/>
       <c r="F52" s="366"/>
@@ -7963,7 +7960,7 @@
         <v/>
       </c>
       <c r="D53" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="365"/>
       <c r="F53" s="366"/>
@@ -7989,7 +7986,7 @@
         <v/>
       </c>
       <c r="D54" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="365"/>
       <c r="F54" s="366"/>
@@ -8015,7 +8012,7 @@
         <v/>
       </c>
       <c r="D55" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="365"/>
       <c r="F55" s="366"/>
@@ -8041,7 +8038,7 @@
         <v/>
       </c>
       <c r="D56" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="365"/>
       <c r="F56" s="366"/>
@@ -8067,7 +8064,7 @@
         <v/>
       </c>
       <c r="D57" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="365"/>
       <c r="F57" s="366"/>
@@ -8093,7 +8090,7 @@
         <v/>
       </c>
       <c r="D58" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="180"/>
       <c r="F58" s="181"/>
@@ -8119,7 +8116,7 @@
         <v/>
       </c>
       <c r="D59" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="180"/>
       <c r="F59" s="181"/>
@@ -8145,7 +8142,7 @@
         <v/>
       </c>
       <c r="D60" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="180"/>
       <c r="F60" s="181"/>
@@ -8171,7 +8168,7 @@
         <v/>
       </c>
       <c r="D61" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="180"/>
       <c r="F61" s="181"/>
@@ -8197,7 +8194,7 @@
         <v/>
       </c>
       <c r="D62" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="180"/>
       <c r="F62" s="181"/>
@@ -8223,7 +8220,7 @@
         <v/>
       </c>
       <c r="D63" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="365"/>
       <c r="F63" s="366"/>
@@ -8249,7 +8246,7 @@
         <v/>
       </c>
       <c r="D64" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="365"/>
       <c r="F64" s="366"/>
@@ -8275,7 +8272,7 @@
         <v/>
       </c>
       <c r="D65" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="365"/>
       <c r="F65" s="366"/>
@@ -8301,7 +8298,7 @@
         <v/>
       </c>
       <c r="D66" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="365"/>
       <c r="F66" s="366"/>
@@ -8327,7 +8324,7 @@
         <v/>
       </c>
       <c r="D67" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="365"/>
       <c r="F67" s="366"/>
@@ -8343,7 +8340,7 @@
     <row r="68" spans="1:14" ht="23.25" customHeight="1" thickBot="1"/>
     <row r="69" spans="1:14" s="37" customFormat="1" ht="59.25" customHeight="1" thickBot="1">
       <c r="B69" s="362" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C69" s="363"/>
       <c r="D69" s="363"/>
@@ -8386,7 +8383,7 @@
       <c r="H71" s="242"/>
       <c r="I71" s="242"/>
       <c r="J71" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K71" s="252"/>
       <c r="L71" s="252"/>
@@ -8503,7 +8500,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="244"/>
       <c r="D78" s="244"/>
@@ -8643,12 +8640,12 @@
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
       <c r="I1" s="176" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
       <c r="L1" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M1" s="30"/>
     </row>
@@ -8750,7 +8747,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="292"/>
       <c r="K7" s="306"/>
@@ -8760,7 +8757,7 @@
     <row r="8" spans="1:25"/>
     <row r="9" spans="1:25" s="37" customFormat="1" ht="21">
       <c r="B9" s="199" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="199"/>
       <c r="D9" s="199"/>
@@ -8778,7 +8775,7 @@
     <row r="10" spans="1:25"/>
     <row r="11" spans="1:25" ht="15.6" customHeight="1">
       <c r="B11" s="269" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="269"/>
       <c r="D11" s="269"/>
@@ -8822,7 +8819,7 @@
     <row r="13" spans="1:25"/>
     <row r="14" spans="1:25">
       <c r="B14" s="269" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="269"/>
       <c r="D14" s="269"/>
@@ -8866,7 +8863,7 @@
     <row r="16" spans="1:25" ht="0" hidden="1" customHeight="1"/>
     <row r="17" spans="1:14">
       <c r="B17" s="177" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" s="177"/>
       <c r="D17" s="177"/>
@@ -8899,7 +8896,7 @@
     <row r="19" spans="1:14"/>
     <row r="20" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B20" s="199" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="199"/>
       <c r="D20" s="199"/>
@@ -8948,7 +8945,7 @@
     <row r="24" spans="1:14"/>
     <row r="25" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B25" s="199" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C25" s="199"/>
       <c r="D25" s="199"/>
@@ -8972,10 +8969,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E27" s="267" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F27" s="267"/>
       <c r="G27" s="267"/>
@@ -9000,10 +8997,10 @@
         <v/>
       </c>
       <c r="D28" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="368" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F28" s="369"/>
       <c r="G28" s="369"/>
@@ -9028,7 +9025,7 @@
         <v/>
       </c>
       <c r="D29" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" s="365"/>
       <c r="F29" s="366"/>
@@ -9054,7 +9051,7 @@
         <v/>
       </c>
       <c r="D30" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="365"/>
       <c r="F30" s="366"/>
@@ -9080,7 +9077,7 @@
         <v/>
       </c>
       <c r="D31" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="365"/>
       <c r="F31" s="366"/>
@@ -9106,7 +9103,7 @@
         <v/>
       </c>
       <c r="D32" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E32" s="365"/>
       <c r="F32" s="366"/>
@@ -9132,7 +9129,7 @@
         <v/>
       </c>
       <c r="D33" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="365"/>
       <c r="F33" s="366"/>
@@ -9158,7 +9155,7 @@
         <v/>
       </c>
       <c r="D34" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="365"/>
       <c r="F34" s="366"/>
@@ -9184,7 +9181,7 @@
         <v/>
       </c>
       <c r="D35" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="365"/>
       <c r="F35" s="366"/>
@@ -9210,7 +9207,7 @@
         <v/>
       </c>
       <c r="D36" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="365"/>
       <c r="F36" s="366"/>
@@ -9236,7 +9233,7 @@
         <v/>
       </c>
       <c r="D37" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="365"/>
       <c r="F37" s="366"/>
@@ -9262,7 +9259,7 @@
         <v/>
       </c>
       <c r="D38" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="365"/>
       <c r="F38" s="366"/>
@@ -9288,7 +9285,7 @@
         <v/>
       </c>
       <c r="D39" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="365"/>
       <c r="F39" s="366"/>
@@ -9314,7 +9311,7 @@
         <v/>
       </c>
       <c r="D40" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="365"/>
       <c r="F40" s="366"/>
@@ -9340,7 +9337,7 @@
         <v/>
       </c>
       <c r="D41" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="365"/>
       <c r="F41" s="366"/>
@@ -9366,7 +9363,7 @@
         <v/>
       </c>
       <c r="D42" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="365"/>
       <c r="F42" s="366"/>
@@ -9392,7 +9389,7 @@
         <v/>
       </c>
       <c r="D43" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="365"/>
       <c r="F43" s="366"/>
@@ -9418,7 +9415,7 @@
         <v/>
       </c>
       <c r="D44" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="365"/>
       <c r="F44" s="366"/>
@@ -9444,7 +9441,7 @@
         <v/>
       </c>
       <c r="D45" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="365"/>
       <c r="F45" s="366"/>
@@ -9470,7 +9467,7 @@
         <v/>
       </c>
       <c r="D46" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="365"/>
       <c r="F46" s="366"/>
@@ -9496,7 +9493,7 @@
         <v/>
       </c>
       <c r="D47" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="365"/>
       <c r="F47" s="366"/>
@@ -9522,7 +9519,7 @@
         <v/>
       </c>
       <c r="D48" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="365"/>
       <c r="F48" s="366"/>
@@ -9548,7 +9545,7 @@
         <v/>
       </c>
       <c r="D49" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="365"/>
       <c r="F49" s="366"/>
@@ -9574,7 +9571,7 @@
         <v/>
       </c>
       <c r="D50" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="365"/>
       <c r="F50" s="366"/>
@@ -9600,7 +9597,7 @@
         <v/>
       </c>
       <c r="D51" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="365"/>
       <c r="F51" s="366"/>
@@ -9626,7 +9623,7 @@
         <v/>
       </c>
       <c r="D52" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="365"/>
       <c r="F52" s="366"/>
@@ -9652,7 +9649,7 @@
         <v/>
       </c>
       <c r="D53" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="365"/>
       <c r="F53" s="366"/>
@@ -9678,7 +9675,7 @@
         <v/>
       </c>
       <c r="D54" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="365"/>
       <c r="F54" s="366"/>
@@ -9704,7 +9701,7 @@
         <v/>
       </c>
       <c r="D55" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="365"/>
       <c r="F55" s="366"/>
@@ -9730,7 +9727,7 @@
         <v/>
       </c>
       <c r="D56" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="365"/>
       <c r="F56" s="366"/>
@@ -9756,7 +9753,7 @@
         <v/>
       </c>
       <c r="D57" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="365"/>
       <c r="F57" s="366"/>
@@ -9782,7 +9779,7 @@
         <v/>
       </c>
       <c r="D58" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="180"/>
       <c r="F58" s="181"/>
@@ -9808,7 +9805,7 @@
         <v/>
       </c>
       <c r="D59" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="180"/>
       <c r="F59" s="181"/>
@@ -9834,7 +9831,7 @@
         <v/>
       </c>
       <c r="D60" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="180"/>
       <c r="F60" s="181"/>
@@ -9860,7 +9857,7 @@
         <v/>
       </c>
       <c r="D61" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="180"/>
       <c r="F61" s="181"/>
@@ -9886,7 +9883,7 @@
         <v/>
       </c>
       <c r="D62" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="180"/>
       <c r="F62" s="181"/>
@@ -9912,7 +9909,7 @@
         <v/>
       </c>
       <c r="D63" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="365"/>
       <c r="F63" s="366"/>
@@ -9938,7 +9935,7 @@
         <v/>
       </c>
       <c r="D64" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="365"/>
       <c r="F64" s="366"/>
@@ -9964,7 +9961,7 @@
         <v/>
       </c>
       <c r="D65" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="365"/>
       <c r="F65" s="366"/>
@@ -9990,7 +9987,7 @@
         <v/>
       </c>
       <c r="D66" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="365"/>
       <c r="F66" s="366"/>
@@ -10016,7 +10013,7 @@
         <v/>
       </c>
       <c r="D67" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="365"/>
       <c r="F67" s="366"/>
@@ -10032,7 +10029,7 @@
     <row r="68" spans="1:14" ht="21.75" customHeight="1" thickBot="1"/>
     <row r="69" spans="1:14" s="37" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B69" s="362" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C69" s="363"/>
       <c r="D69" s="363"/>
@@ -10075,7 +10072,7 @@
       <c r="H71" s="242"/>
       <c r="I71" s="242"/>
       <c r="J71" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K71" s="252"/>
       <c r="L71" s="252"/>
@@ -10192,7 +10189,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="244"/>
       <c r="D78" s="244"/>
@@ -11260,7 +11257,7 @@
     </row>
     <row r="49" spans="2:182" ht="30.75" customHeight="1">
       <c r="B49" s="195" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C49" s="195"/>
       <c r="D49" s="38">
@@ -11413,7 +11410,7 @@
     </row>
     <row r="57" spans="2:182" ht="30.75" customHeight="1">
       <c r="B57" s="195" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C57" s="195"/>
       <c r="D57" s="38">
@@ -11566,7 +11563,7 @@
     </row>
     <row r="65" spans="2:182" ht="30.75" customHeight="1">
       <c r="B65" s="195" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C65" s="195"/>
       <c r="D65" s="38">
@@ -12501,7 +12498,7 @@
       <c r="B36" s="63"/>
       <c r="C36" s="66"/>
       <c r="D36" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="67"/>
       <c r="F36" s="68" t="s">
@@ -12511,16 +12508,16 @@
         <v>67</v>
       </c>
       <c r="H36" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I36" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J36" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K36" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L36" s="68"/>
       <c r="M36" s="218"/>
@@ -12535,7 +12532,7 @@
       <c r="B37" s="63"/>
       <c r="C37" s="66"/>
       <c r="D37" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="67"/>
       <c r="F37" s="68" t="s">
@@ -12545,16 +12542,16 @@
         <v>67</v>
       </c>
       <c r="H37" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I37" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J37" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K37" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L37" s="68"/>
       <c r="M37" s="218"/>
@@ -12569,7 +12566,7 @@
       <c r="B38" s="63"/>
       <c r="C38" s="66"/>
       <c r="D38" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="67"/>
       <c r="F38" s="68" t="s">
@@ -12579,16 +12576,16 @@
         <v>67</v>
       </c>
       <c r="H38" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I38" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J38" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K38" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L38" s="68"/>
       <c r="M38" s="218"/>
@@ -12603,7 +12600,7 @@
       <c r="B39" s="63"/>
       <c r="C39" s="66"/>
       <c r="D39" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="67"/>
       <c r="F39" s="68" t="s">
@@ -12613,16 +12610,16 @@
         <v>67</v>
       </c>
       <c r="H39" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I39" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J39" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K39" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L39" s="68"/>
       <c r="M39" s="218"/>
@@ -12637,7 +12634,7 @@
       <c r="B40" s="63"/>
       <c r="C40" s="66"/>
       <c r="D40" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="67"/>
       <c r="F40" s="68" t="s">
@@ -12647,16 +12644,16 @@
         <v>67</v>
       </c>
       <c r="H40" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I40" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J40" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K40" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L40" s="68"/>
       <c r="M40" s="218"/>
@@ -12671,7 +12668,7 @@
       <c r="B41" s="63"/>
       <c r="C41" s="66"/>
       <c r="D41" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="67"/>
       <c r="F41" s="68" t="s">
@@ -12681,16 +12678,16 @@
         <v>67</v>
       </c>
       <c r="H41" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I41" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J41" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K41" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L41" s="68"/>
       <c r="M41" s="218"/>
@@ -12705,7 +12702,7 @@
       <c r="B42" s="63"/>
       <c r="C42" s="66"/>
       <c r="D42" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="67"/>
       <c r="F42" s="68" t="s">
@@ -12715,16 +12712,16 @@
         <v>67</v>
       </c>
       <c r="H42" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I42" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J42" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K42" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L42" s="68"/>
       <c r="M42" s="218"/>
@@ -12739,7 +12736,7 @@
       <c r="B43" s="63"/>
       <c r="C43" s="66"/>
       <c r="D43" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="67"/>
       <c r="F43" s="68" t="s">
@@ -12749,16 +12746,16 @@
         <v>67</v>
       </c>
       <c r="H43" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I43" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J43" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K43" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L43" s="68"/>
       <c r="M43" s="218"/>
@@ -12773,7 +12770,7 @@
       <c r="B44" s="63"/>
       <c r="C44" s="66"/>
       <c r="D44" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="67"/>
       <c r="F44" s="68" t="s">
@@ -12783,16 +12780,16 @@
         <v>67</v>
       </c>
       <c r="H44" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I44" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J44" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K44" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L44" s="68"/>
       <c r="M44" s="218"/>
@@ -12807,7 +12804,7 @@
       <c r="B45" s="63"/>
       <c r="C45" s="66"/>
       <c r="D45" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="67"/>
       <c r="F45" s="68" t="s">
@@ -12817,16 +12814,16 @@
         <v>67</v>
       </c>
       <c r="H45" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I45" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J45" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K45" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L45" s="68"/>
       <c r="M45" s="218"/>
@@ -12841,7 +12838,7 @@
       <c r="B46" s="63"/>
       <c r="C46" s="66"/>
       <c r="D46" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="67"/>
       <c r="F46" s="68" t="s">
@@ -12851,16 +12848,16 @@
         <v>67</v>
       </c>
       <c r="H46" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I46" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J46" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K46" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L46" s="68"/>
       <c r="M46" s="218"/>
@@ -12875,7 +12872,7 @@
       <c r="B47" s="63"/>
       <c r="C47" s="66"/>
       <c r="D47" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="67"/>
       <c r="F47" s="68" t="s">
@@ -12885,16 +12882,16 @@
         <v>67</v>
       </c>
       <c r="H47" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I47" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J47" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K47" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L47" s="68"/>
       <c r="M47" s="218"/>
@@ -12909,7 +12906,7 @@
       <c r="B48" s="63"/>
       <c r="C48" s="66"/>
       <c r="D48" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="67"/>
       <c r="F48" s="68" t="s">
@@ -12919,16 +12916,16 @@
         <v>67</v>
       </c>
       <c r="H48" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I48" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J48" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K48" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L48" s="68"/>
       <c r="M48" s="218"/>
@@ -12943,7 +12940,7 @@
       <c r="B49" s="63"/>
       <c r="C49" s="66"/>
       <c r="D49" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="67"/>
       <c r="F49" s="68" t="s">
@@ -12953,16 +12950,16 @@
         <v>67</v>
       </c>
       <c r="H49" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I49" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J49" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K49" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L49" s="68"/>
       <c r="M49" s="218"/>
@@ -12977,7 +12974,7 @@
       <c r="B50" s="63"/>
       <c r="C50" s="66"/>
       <c r="D50" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="67"/>
       <c r="F50" s="68" t="s">
@@ -12987,16 +12984,16 @@
         <v>67</v>
       </c>
       <c r="H50" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I50" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J50" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K50" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L50" s="68"/>
       <c r="M50" s="218"/>
@@ -13011,7 +13008,7 @@
       <c r="B51" s="63"/>
       <c r="C51" s="66"/>
       <c r="D51" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="67"/>
       <c r="F51" s="68" t="s">
@@ -13021,16 +13018,16 @@
         <v>67</v>
       </c>
       <c r="H51" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I51" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J51" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K51" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L51" s="68"/>
       <c r="M51" s="218"/>
@@ -13045,7 +13042,7 @@
       <c r="B52" s="63"/>
       <c r="C52" s="66"/>
       <c r="D52" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="67"/>
       <c r="F52" s="68" t="s">
@@ -13055,16 +13052,16 @@
         <v>67</v>
       </c>
       <c r="H52" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I52" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J52" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K52" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L52" s="68"/>
       <c r="M52" s="218"/>
@@ -13079,7 +13076,7 @@
       <c r="B53" s="63"/>
       <c r="C53" s="66"/>
       <c r="D53" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="67"/>
       <c r="F53" s="68" t="s">
@@ -13089,16 +13086,16 @@
         <v>67</v>
       </c>
       <c r="H53" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I53" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J53" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K53" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L53" s="68"/>
       <c r="M53" s="218"/>
@@ -13113,7 +13110,7 @@
       <c r="B54" s="63"/>
       <c r="C54" s="66"/>
       <c r="D54" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="67"/>
       <c r="F54" s="68" t="s">
@@ -13123,16 +13120,16 @@
         <v>67</v>
       </c>
       <c r="H54" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I54" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J54" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K54" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L54" s="68"/>
       <c r="M54" s="218"/>
@@ -13147,7 +13144,7 @@
       <c r="B55" s="63"/>
       <c r="C55" s="66"/>
       <c r="D55" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="67"/>
       <c r="F55" s="68" t="s">
@@ -13157,16 +13154,16 @@
         <v>67</v>
       </c>
       <c r="H55" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I55" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J55" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K55" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L55" s="68"/>
       <c r="M55" s="218"/>
@@ -13181,7 +13178,7 @@
       <c r="B56" s="63"/>
       <c r="C56" s="66"/>
       <c r="D56" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="67"/>
       <c r="F56" s="68" t="s">
@@ -13191,16 +13188,16 @@
         <v>67</v>
       </c>
       <c r="H56" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I56" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J56" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K56" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L56" s="68"/>
       <c r="M56" s="218"/>
@@ -13215,7 +13212,7 @@
       <c r="B57" s="63"/>
       <c r="C57" s="66"/>
       <c r="D57" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="67"/>
       <c r="F57" s="68" t="s">
@@ -13225,16 +13222,16 @@
         <v>67</v>
       </c>
       <c r="H57" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I57" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J57" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K57" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L57" s="68"/>
       <c r="M57" s="218"/>
@@ -13249,7 +13246,7 @@
       <c r="B58" s="63"/>
       <c r="C58" s="66"/>
       <c r="D58" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="67"/>
       <c r="F58" s="68" t="s">
@@ -13259,16 +13256,16 @@
         <v>67</v>
       </c>
       <c r="H58" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I58" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J58" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K58" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L58" s="68"/>
       <c r="M58" s="218"/>
@@ -13283,7 +13280,7 @@
       <c r="B59" s="63"/>
       <c r="C59" s="66"/>
       <c r="D59" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="67"/>
       <c r="F59" s="68" t="s">
@@ -13293,16 +13290,16 @@
         <v>67</v>
       </c>
       <c r="H59" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I59" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J59" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K59" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L59" s="68"/>
       <c r="M59" s="218"/>
@@ -13317,7 +13314,7 @@
       <c r="B60" s="63"/>
       <c r="C60" s="66"/>
       <c r="D60" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="67"/>
       <c r="F60" s="68" t="s">
@@ -13327,16 +13324,16 @@
         <v>67</v>
       </c>
       <c r="H60" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I60" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J60" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K60" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L60" s="68"/>
       <c r="M60" s="218"/>
@@ -13351,7 +13348,7 @@
       <c r="B61" s="63"/>
       <c r="C61" s="66"/>
       <c r="D61" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="67"/>
       <c r="F61" s="68" t="s">
@@ -13361,16 +13358,16 @@
         <v>67</v>
       </c>
       <c r="H61" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I61" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J61" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K61" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L61" s="68"/>
       <c r="M61" s="218"/>
@@ -13385,7 +13382,7 @@
       <c r="B62" s="63"/>
       <c r="C62" s="66"/>
       <c r="D62" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="67"/>
       <c r="F62" s="68" t="s">
@@ -13395,16 +13392,16 @@
         <v>67</v>
       </c>
       <c r="H62" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I62" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J62" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K62" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L62" s="68"/>
       <c r="M62" s="218"/>
@@ -13419,7 +13416,7 @@
       <c r="B63" s="63"/>
       <c r="C63" s="66"/>
       <c r="D63" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="67"/>
       <c r="F63" s="68" t="s">
@@ -13429,16 +13426,16 @@
         <v>67</v>
       </c>
       <c r="H63" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I63" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J63" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K63" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L63" s="68"/>
       <c r="M63" s="218"/>
@@ -13453,7 +13450,7 @@
       <c r="B64" s="63"/>
       <c r="C64" s="66"/>
       <c r="D64" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="67"/>
       <c r="F64" s="68" t="s">
@@ -13463,16 +13460,16 @@
         <v>67</v>
       </c>
       <c r="H64" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I64" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J64" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K64" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L64" s="68"/>
       <c r="M64" s="218"/>
@@ -13487,7 +13484,7 @@
       <c r="B65" s="63"/>
       <c r="C65" s="66"/>
       <c r="D65" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="67"/>
       <c r="F65" s="68" t="s">
@@ -13497,16 +13494,16 @@
         <v>67</v>
       </c>
       <c r="H65" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I65" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J65" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K65" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L65" s="68"/>
       <c r="M65" s="218"/>
@@ -13521,7 +13518,7 @@
       <c r="B66" s="63"/>
       <c r="C66" s="66"/>
       <c r="D66" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="67"/>
       <c r="F66" s="68" t="s">
@@ -13531,16 +13528,16 @@
         <v>67</v>
       </c>
       <c r="H66" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I66" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J66" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K66" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L66" s="68"/>
       <c r="M66" s="218"/>
@@ -13555,7 +13552,7 @@
       <c r="B67" s="63"/>
       <c r="C67" s="66"/>
       <c r="D67" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="67"/>
       <c r="F67" s="68" t="s">
@@ -13565,16 +13562,16 @@
         <v>67</v>
       </c>
       <c r="H67" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I67" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J67" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K67" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L67" s="68"/>
       <c r="M67" s="218"/>
@@ -13589,7 +13586,7 @@
       <c r="B68" s="63"/>
       <c r="C68" s="66"/>
       <c r="D68" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E68" s="67"/>
       <c r="F68" s="68" t="s">
@@ -13599,16 +13596,16 @@
         <v>67</v>
       </c>
       <c r="H68" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I68" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J68" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K68" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L68" s="68"/>
       <c r="M68" s="218"/>
@@ -13623,7 +13620,7 @@
       <c r="B69" s="63"/>
       <c r="C69" s="66"/>
       <c r="D69" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E69" s="67"/>
       <c r="F69" s="68" t="s">
@@ -13633,16 +13630,16 @@
         <v>67</v>
       </c>
       <c r="H69" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I69" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J69" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K69" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L69" s="68"/>
       <c r="M69" s="218"/>
@@ -13657,7 +13654,7 @@
       <c r="B70" s="63"/>
       <c r="C70" s="66"/>
       <c r="D70" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E70" s="67"/>
       <c r="F70" s="68" t="s">
@@ -13667,16 +13664,16 @@
         <v>67</v>
       </c>
       <c r="H70" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I70" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J70" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K70" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L70" s="68"/>
       <c r="M70" s="218"/>
@@ -13691,7 +13688,7 @@
       <c r="B71" s="63"/>
       <c r="C71" s="66"/>
       <c r="D71" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E71" s="67"/>
       <c r="F71" s="68" t="s">
@@ -13701,16 +13698,16 @@
         <v>67</v>
       </c>
       <c r="H71" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I71" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J71" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K71" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L71" s="68"/>
       <c r="M71" s="218"/>
@@ -13725,7 +13722,7 @@
       <c r="B72" s="63"/>
       <c r="C72" s="66"/>
       <c r="D72" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E72" s="67"/>
       <c r="F72" s="68" t="s">
@@ -13735,16 +13732,16 @@
         <v>67</v>
       </c>
       <c r="H72" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I72" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J72" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K72" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L72" s="68"/>
       <c r="M72" s="218"/>
@@ -13759,7 +13756,7 @@
       <c r="B73" s="63"/>
       <c r="C73" s="66"/>
       <c r="D73" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E73" s="67"/>
       <c r="F73" s="68" t="s">
@@ -13769,16 +13766,16 @@
         <v>67</v>
       </c>
       <c r="H73" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I73" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J73" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K73" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L73" s="68"/>
       <c r="M73" s="218"/>
@@ -13793,7 +13790,7 @@
       <c r="B74" s="63"/>
       <c r="C74" s="66"/>
       <c r="D74" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E74" s="67"/>
       <c r="F74" s="68" t="s">
@@ -13803,16 +13800,16 @@
         <v>67</v>
       </c>
       <c r="H74" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I74" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J74" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K74" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L74" s="68"/>
       <c r="M74" s="218"/>
@@ -13827,7 +13824,7 @@
       <c r="B75" s="63"/>
       <c r="C75" s="66"/>
       <c r="D75" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E75" s="67"/>
       <c r="F75" s="68" t="s">
@@ -13837,16 +13834,16 @@
         <v>67</v>
       </c>
       <c r="H75" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I75" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J75" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K75" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L75" s="68"/>
       <c r="M75" s="218"/>
@@ -13857,7 +13854,7 @@
     <row r="76" spans="1:16" ht="26.25" customHeight="1"/>
     <row r="77" spans="1:16" s="46" customFormat="1" ht="26.25" customHeight="1">
       <c r="B77" s="215" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C77" s="216"/>
       <c r="D77" s="216"/>
@@ -13906,7 +13903,7 @@
       <c r="J79" s="205"/>
       <c r="K79" s="205"/>
       <c r="L79" s="206" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M79" s="207"/>
       <c r="N79" s="207"/>
@@ -14035,7 +14032,7 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="204" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B86" s="204"/>
       <c r="C86" s="204"/>
@@ -14450,7 +14447,7 @@
     <row r="16" spans="2:14" ht="27" customHeight="1"/>
     <row r="17" spans="2:14">
       <c r="B17" s="269" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="269"/>
       <c r="D17" s="269"/>
@@ -14521,7 +14518,7 @@
     <row r="23" spans="2:14" ht="27" customHeight="1"/>
     <row r="24" spans="2:14" s="37" customFormat="1" ht="21">
       <c r="B24" s="273" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="274"/>
       <c r="D24" s="274"/>
@@ -14538,7 +14535,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G25" s="75"/>
       <c r="H25" s="75"/>
@@ -14551,7 +14548,7 @@
     </row>
     <row r="26" spans="2:14" ht="19.5" customHeight="1">
       <c r="B26" s="276" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" s="276"/>
       <c r="D26" s="54">
@@ -14562,7 +14559,7 @@
         <v>40</v>
       </c>
       <c r="G26" s="277" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26" s="278"/>
       <c r="I26" s="278"/>
@@ -14596,7 +14593,7 @@
     </row>
     <row r="28" spans="2:14" ht="19.5" customHeight="1">
       <c r="B28" s="276" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" s="276"/>
       <c r="D28" s="56">
@@ -14617,7 +14614,7 @@
     </row>
     <row r="29" spans="2:14" ht="19.5" customHeight="1">
       <c r="B29" s="276" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" s="276"/>
       <c r="D29" s="56">
@@ -14638,7 +14635,7 @@
     </row>
     <row r="30" spans="2:14" ht="19.5" customHeight="1">
       <c r="B30" s="276" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="276"/>
       <c r="D30" s="56">
@@ -14659,7 +14656,7 @@
     </row>
     <row r="31" spans="2:14" ht="19.5" customHeight="1" thickBot="1">
       <c r="B31" s="276" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="276"/>
       <c r="D31" s="80">
@@ -14723,7 +14720,7 @@
         <v>57</v>
       </c>
       <c r="E35" s="267" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F35" s="267"/>
       <c r="G35" s="267"/>
@@ -14748,7 +14745,7 @@
         <v/>
       </c>
       <c r="D36" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="264"/>
       <c r="F36" s="265"/>
@@ -14774,7 +14771,7 @@
         <v/>
       </c>
       <c r="D37" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="264"/>
       <c r="F37" s="265"/>
@@ -14800,7 +14797,7 @@
         <v/>
       </c>
       <c r="D38" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="264"/>
       <c r="F38" s="265"/>
@@ -14826,7 +14823,7 @@
         <v/>
       </c>
       <c r="D39" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="264"/>
       <c r="F39" s="265"/>
@@ -14852,7 +14849,7 @@
         <v/>
       </c>
       <c r="D40" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="264"/>
       <c r="F40" s="265"/>
@@ -14878,7 +14875,7 @@
         <v/>
       </c>
       <c r="D41" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="264"/>
       <c r="F41" s="265"/>
@@ -14904,7 +14901,7 @@
         <v/>
       </c>
       <c r="D42" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="264"/>
       <c r="F42" s="265"/>
@@ -14930,7 +14927,7 @@
         <v/>
       </c>
       <c r="D43" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="264"/>
       <c r="F43" s="265"/>
@@ -14956,7 +14953,7 @@
         <v/>
       </c>
       <c r="D44" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="264"/>
       <c r="F44" s="265"/>
@@ -14982,7 +14979,7 @@
         <v/>
       </c>
       <c r="D45" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="264"/>
       <c r="F45" s="265"/>
@@ -15008,7 +15005,7 @@
         <v/>
       </c>
       <c r="D46" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="264"/>
       <c r="F46" s="265"/>
@@ -15034,7 +15031,7 @@
         <v/>
       </c>
       <c r="D47" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="264"/>
       <c r="F47" s="265"/>
@@ -15060,7 +15057,7 @@
         <v/>
       </c>
       <c r="D48" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="264"/>
       <c r="F48" s="265"/>
@@ -15086,7 +15083,7 @@
         <v/>
       </c>
       <c r="D49" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="264"/>
       <c r="F49" s="265"/>
@@ -15112,7 +15109,7 @@
         <v/>
       </c>
       <c r="D50" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="264"/>
       <c r="F50" s="265"/>
@@ -15138,7 +15135,7 @@
         <v/>
       </c>
       <c r="D51" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="264"/>
       <c r="F51" s="265"/>
@@ -15164,7 +15161,7 @@
         <v/>
       </c>
       <c r="D52" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="264"/>
       <c r="F52" s="265"/>
@@ -15190,7 +15187,7 @@
         <v/>
       </c>
       <c r="D53" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="264"/>
       <c r="F53" s="265"/>
@@ -15216,7 +15213,7 @@
         <v/>
       </c>
       <c r="D54" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="264"/>
       <c r="F54" s="265"/>
@@ -15242,7 +15239,7 @@
         <v/>
       </c>
       <c r="D55" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="264"/>
       <c r="F55" s="265"/>
@@ -15268,7 +15265,7 @@
         <v/>
       </c>
       <c r="D56" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="264"/>
       <c r="F56" s="265"/>
@@ -15294,7 +15291,7 @@
         <v/>
       </c>
       <c r="D57" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="264"/>
       <c r="F57" s="265"/>
@@ -15320,7 +15317,7 @@
         <v/>
       </c>
       <c r="D58" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="264"/>
       <c r="F58" s="265"/>
@@ -15346,7 +15343,7 @@
         <v/>
       </c>
       <c r="D59" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="264"/>
       <c r="F59" s="265"/>
@@ -15372,7 +15369,7 @@
         <v/>
       </c>
       <c r="D60" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="264"/>
       <c r="F60" s="265"/>
@@ -15398,7 +15395,7 @@
         <v/>
       </c>
       <c r="D61" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="264"/>
       <c r="F61" s="265"/>
@@ -15424,7 +15421,7 @@
         <v/>
       </c>
       <c r="D62" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="264"/>
       <c r="F62" s="265"/>
@@ -15450,7 +15447,7 @@
         <v/>
       </c>
       <c r="D63" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="264"/>
       <c r="F63" s="265"/>
@@ -15476,7 +15473,7 @@
         <v/>
       </c>
       <c r="D64" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="264"/>
       <c r="F64" s="265"/>
@@ -15502,7 +15499,7 @@
         <v/>
       </c>
       <c r="D65" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="264"/>
       <c r="F65" s="265"/>
@@ -15528,7 +15525,7 @@
         <v/>
       </c>
       <c r="D66" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="82"/>
       <c r="F66" s="83"/>
@@ -15554,7 +15551,7 @@
         <v/>
       </c>
       <c r="D67" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="82"/>
       <c r="F67" s="83"/>
@@ -15580,7 +15577,7 @@
         <v/>
       </c>
       <c r="D68" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E68" s="82"/>
       <c r="F68" s="83"/>
@@ -15606,7 +15603,7 @@
         <v/>
       </c>
       <c r="D69" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E69" s="82"/>
       <c r="F69" s="83"/>
@@ -15632,7 +15629,7 @@
         <v/>
       </c>
       <c r="D70" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E70" s="82"/>
       <c r="F70" s="83"/>
@@ -15658,7 +15655,7 @@
         <v/>
       </c>
       <c r="D71" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E71" s="264"/>
       <c r="F71" s="265"/>
@@ -15684,7 +15681,7 @@
         <v/>
       </c>
       <c r="D72" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E72" s="264"/>
       <c r="F72" s="265"/>
@@ -15710,7 +15707,7 @@
         <v/>
       </c>
       <c r="D73" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E73" s="264"/>
       <c r="F73" s="265"/>
@@ -15736,7 +15733,7 @@
         <v/>
       </c>
       <c r="D74" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E74" s="264"/>
       <c r="F74" s="265"/>
@@ -15762,7 +15759,7 @@
         <v/>
       </c>
       <c r="D75" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E75" s="264"/>
       <c r="F75" s="265"/>
@@ -15778,7 +15775,7 @@
     <row r="76" spans="1:14" ht="36" customHeight="1" thickBot="1"/>
     <row r="77" spans="1:14" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B77" s="248" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="249"/>
       <c r="D77" s="249"/>
@@ -15803,10 +15800,10 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="K78" s="85" t="s">
         <v>83</v>
-      </c>
-      <c r="K78" s="85" t="s">
-        <v>84</v>
       </c>
       <c r="L78" s="85"/>
       <c r="M78" s="85"/>
@@ -15969,7 +15966,7 @@
     </row>
     <row r="87" spans="1:14" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B87" s="248" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C87" s="249"/>
       <c r="D87" s="249"/>
@@ -16012,7 +16009,7 @@
       <c r="H89" s="242"/>
       <c r="I89" s="242"/>
       <c r="J89" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K89" s="252"/>
       <c r="L89" s="252"/>
@@ -16129,7 +16126,7 @@
     </row>
     <row r="96" spans="1:14">
       <c r="B96" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C96" s="244"/>
       <c r="D96" s="244"/>
@@ -16524,7 +16521,7 @@
     <row r="16" spans="2:14" ht="27" customHeight="1"/>
     <row r="17" spans="2:14">
       <c r="B17" s="269" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="269"/>
       <c r="D17" s="269"/>
@@ -16605,7 +16602,7 @@
     <row r="23" spans="2:14" ht="27" customHeight="1"/>
     <row r="24" spans="2:14" s="93" customFormat="1" ht="21">
       <c r="B24" s="199" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="199"/>
       <c r="D24" s="199"/>
@@ -16622,7 +16619,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25" s="94"/>
       <c r="D25" s="94"/>
@@ -16639,7 +16636,7 @@
     </row>
     <row r="26" spans="2:14" ht="18.75" customHeight="1">
       <c r="B26" s="276" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" s="276"/>
       <c r="D26" s="54">
@@ -16651,15 +16648,15 @@
       </c>
       <c r="F26" s="94"/>
       <c r="G26" s="96" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" s="97"/>
       <c r="J26" s="97"/>
       <c r="L26" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="M26" s="99" t="s">
         <v>87</v>
-      </c>
-      <c r="M26" s="99" t="s">
-        <v>88</v>
       </c>
       <c r="N26" s="81"/>
     </row>
@@ -16678,7 +16675,7 @@
       </c>
       <c r="F27" s="94"/>
       <c r="G27" s="100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H27" s="101"/>
       <c r="I27" s="101"/>
@@ -16695,7 +16692,7 @@
     </row>
     <row r="28" spans="2:14" ht="18.75" customHeight="1">
       <c r="B28" s="276" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" s="276"/>
       <c r="D28" s="56">
@@ -16707,7 +16704,7 @@
       </c>
       <c r="F28" s="94"/>
       <c r="G28" s="303" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H28" s="303"/>
       <c r="I28" s="303"/>
@@ -16719,7 +16716,7 @@
     </row>
     <row r="29" spans="2:14" ht="18.75" customHeight="1">
       <c r="B29" s="276" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" s="276"/>
       <c r="D29" s="56">
@@ -16736,16 +16733,16 @@
       <c r="J29" s="303"/>
       <c r="K29" s="303"/>
       <c r="L29" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="M29" s="99" t="s">
         <v>87</v>
-      </c>
-      <c r="M29" s="99" t="s">
-        <v>88</v>
       </c>
       <c r="N29" s="81"/>
     </row>
     <row r="30" spans="2:14" ht="18.75" customHeight="1">
       <c r="B30" s="276" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="276"/>
       <c r="D30" s="56">
@@ -16757,7 +16754,7 @@
       </c>
       <c r="F30" s="94"/>
       <c r="G30" s="100" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H30" s="101"/>
       <c r="I30" s="106"/>
@@ -16774,7 +16771,7 @@
     </row>
     <row r="31" spans="2:14" ht="18.75" customHeight="1">
       <c r="B31" s="276" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="276"/>
       <c r="D31" s="80">
@@ -16786,7 +16783,7 @@
       </c>
       <c r="F31" s="94"/>
       <c r="G31" s="300" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H31" s="301"/>
       <c r="I31" s="301"/>
@@ -16814,7 +16811,7 @@
     <row r="33" spans="1:14" ht="18.75" customHeight="1">
       <c r="B33" s="77"/>
       <c r="C33" s="294" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D33" s="295"/>
       <c r="E33" s="295"/>
@@ -16870,10 +16867,10 @@
         <v>56</v>
       </c>
       <c r="D38" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="267" t="s">
         <v>93</v>
-      </c>
-      <c r="E38" s="267" t="s">
-        <v>94</v>
       </c>
       <c r="F38" s="267"/>
       <c r="G38" s="267"/>
@@ -16898,7 +16895,7 @@
         <v/>
       </c>
       <c r="D39" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="264"/>
       <c r="F39" s="265"/>
@@ -16924,7 +16921,7 @@
         <v/>
       </c>
       <c r="D40" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="264"/>
       <c r="F40" s="265"/>
@@ -16950,7 +16947,7 @@
         <v/>
       </c>
       <c r="D41" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="264"/>
       <c r="F41" s="265"/>
@@ -16976,7 +16973,7 @@
         <v/>
       </c>
       <c r="D42" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="264"/>
       <c r="F42" s="265"/>
@@ -17002,7 +16999,7 @@
         <v/>
       </c>
       <c r="D43" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="264"/>
       <c r="F43" s="265"/>
@@ -17028,7 +17025,7 @@
         <v/>
       </c>
       <c r="D44" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="264"/>
       <c r="F44" s="265"/>
@@ -17054,7 +17051,7 @@
         <v/>
       </c>
       <c r="D45" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="264"/>
       <c r="F45" s="265"/>
@@ -17080,7 +17077,7 @@
         <v/>
       </c>
       <c r="D46" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="264"/>
       <c r="F46" s="265"/>
@@ -17106,7 +17103,7 @@
         <v/>
       </c>
       <c r="D47" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="264"/>
       <c r="F47" s="265"/>
@@ -17132,7 +17129,7 @@
         <v/>
       </c>
       <c r="D48" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="264"/>
       <c r="F48" s="265"/>
@@ -17158,7 +17155,7 @@
         <v/>
       </c>
       <c r="D49" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="264"/>
       <c r="F49" s="265"/>
@@ -17184,7 +17181,7 @@
         <v/>
       </c>
       <c r="D50" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="264"/>
       <c r="F50" s="265"/>
@@ -17210,7 +17207,7 @@
         <v/>
       </c>
       <c r="D51" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="264"/>
       <c r="F51" s="265"/>
@@ -17236,7 +17233,7 @@
         <v/>
       </c>
       <c r="D52" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="264"/>
       <c r="F52" s="265"/>
@@ -17262,7 +17259,7 @@
         <v/>
       </c>
       <c r="D53" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="264"/>
       <c r="F53" s="265"/>
@@ -17288,7 +17285,7 @@
         <v/>
       </c>
       <c r="D54" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="264"/>
       <c r="F54" s="265"/>
@@ -17314,7 +17311,7 @@
         <v/>
       </c>
       <c r="D55" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="264"/>
       <c r="F55" s="265"/>
@@ -17340,7 +17337,7 @@
         <v/>
       </c>
       <c r="D56" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="264"/>
       <c r="F56" s="265"/>
@@ -17366,7 +17363,7 @@
         <v/>
       </c>
       <c r="D57" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="264"/>
       <c r="F57" s="265"/>
@@ -17392,7 +17389,7 @@
         <v/>
       </c>
       <c r="D58" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="264"/>
       <c r="F58" s="265"/>
@@ -17418,7 +17415,7 @@
         <v/>
       </c>
       <c r="D59" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="264"/>
       <c r="F59" s="265"/>
@@ -17444,7 +17441,7 @@
         <v/>
       </c>
       <c r="D60" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="264"/>
       <c r="F60" s="265"/>
@@ -17470,7 +17467,7 @@
         <v/>
       </c>
       <c r="D61" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="264"/>
       <c r="F61" s="265"/>
@@ -17496,7 +17493,7 @@
         <v/>
       </c>
       <c r="D62" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="264"/>
       <c r="F62" s="265"/>
@@ -17522,7 +17519,7 @@
         <v/>
       </c>
       <c r="D63" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="264"/>
       <c r="F63" s="265"/>
@@ -17548,7 +17545,7 @@
         <v/>
       </c>
       <c r="D64" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="264"/>
       <c r="F64" s="265"/>
@@ -17574,7 +17571,7 @@
         <v/>
       </c>
       <c r="D65" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="264"/>
       <c r="F65" s="265"/>
@@ -17600,7 +17597,7 @@
         <v/>
       </c>
       <c r="D66" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="264"/>
       <c r="F66" s="265"/>
@@ -17626,7 +17623,7 @@
         <v/>
       </c>
       <c r="D67" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="264"/>
       <c r="F67" s="265"/>
@@ -17652,7 +17649,7 @@
         <v/>
       </c>
       <c r="D68" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E68" s="264"/>
       <c r="F68" s="265"/>
@@ -17678,7 +17675,7 @@
         <v/>
       </c>
       <c r="D69" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E69" s="82"/>
       <c r="F69" s="83"/>
@@ -17704,7 +17701,7 @@
         <v/>
       </c>
       <c r="D70" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E70" s="82"/>
       <c r="F70" s="83"/>
@@ -17730,7 +17727,7 @@
         <v/>
       </c>
       <c r="D71" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E71" s="82"/>
       <c r="F71" s="83"/>
@@ -17756,7 +17753,7 @@
         <v/>
       </c>
       <c r="D72" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E72" s="82"/>
       <c r="F72" s="83"/>
@@ -17782,7 +17779,7 @@
         <v/>
       </c>
       <c r="D73" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E73" s="82"/>
       <c r="F73" s="83"/>
@@ -17808,7 +17805,7 @@
         <v/>
       </c>
       <c r="D74" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E74" s="264"/>
       <c r="F74" s="265"/>
@@ -17834,7 +17831,7 @@
         <v/>
       </c>
       <c r="D75" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E75" s="264"/>
       <c r="F75" s="265"/>
@@ -17860,7 +17857,7 @@
         <v/>
       </c>
       <c r="D76" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E76" s="264"/>
       <c r="F76" s="265"/>
@@ -17886,7 +17883,7 @@
         <v/>
       </c>
       <c r="D77" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E77" s="264"/>
       <c r="F77" s="265"/>
@@ -17912,7 +17909,7 @@
         <v/>
       </c>
       <c r="D78" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E78" s="264"/>
       <c r="F78" s="265"/>
@@ -17928,7 +17925,7 @@
     <row r="79" spans="1:14" ht="27" customHeight="1"/>
     <row r="80" spans="1:14" s="93" customFormat="1" ht="21">
       <c r="B80" s="288" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C80" s="289"/>
       <c r="D80" s="289"/>
@@ -17953,10 +17950,10 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="K81" s="293" t="s">
         <v>83</v>
-      </c>
-      <c r="K81" s="293" t="s">
-        <v>84</v>
       </c>
       <c r="L81" s="293"/>
       <c r="M81" s="293"/>
@@ -18119,7 +18116,7 @@
     </row>
     <row r="90" spans="1:14" s="93" customFormat="1" ht="21">
       <c r="B90" s="288" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C90" s="289"/>
       <c r="D90" s="289"/>
@@ -18154,7 +18151,7 @@
         <v>1</v>
       </c>
       <c r="B92" s="242" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C92" s="242"/>
       <c r="D92" s="242"/>
@@ -18164,7 +18161,7 @@
       <c r="H92" s="242"/>
       <c r="I92" s="242"/>
       <c r="J92" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K92" s="252"/>
       <c r="L92" s="252"/>
@@ -18176,7 +18173,7 @@
         <v>2</v>
       </c>
       <c r="B93" s="242" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C93" s="242"/>
       <c r="D93" s="242"/>
@@ -18196,7 +18193,7 @@
         <v>3</v>
       </c>
       <c r="B94" s="242" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C94" s="242"/>
       <c r="D94" s="242"/>
@@ -18216,7 +18213,7 @@
         <v>4</v>
       </c>
       <c r="B95" s="242" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C95" s="242"/>
       <c r="D95" s="242"/>
@@ -18236,7 +18233,7 @@
         <v>5</v>
       </c>
       <c r="B96" s="242" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C96" s="242"/>
       <c r="D96" s="242"/>
@@ -18256,7 +18253,7 @@
         <v>6</v>
       </c>
       <c r="B97" s="242" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C97" s="242"/>
       <c r="D97" s="242"/>
@@ -18276,7 +18273,7 @@
         <v>7</v>
       </c>
       <c r="B98" s="242" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C98" s="242"/>
       <c r="D98" s="242"/>
@@ -18293,7 +18290,7 @@
     </row>
     <row r="99" spans="1:14">
       <c r="B99" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C99" s="244"/>
       <c r="D99" s="244"/>
@@ -18572,11 +18569,11 @@
       <c r="H6" s="200"/>
       <c r="I6" s="200"/>
       <c r="J6" s="318" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K6" s="318"/>
       <c r="L6" s="202" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M6" s="202"/>
       <c r="N6" s="202"/>
@@ -18593,7 +18590,7 @@
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="J7" s="319" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="319"/>
       <c r="L7" s="292"/>
@@ -18604,7 +18601,7 @@
     <row r="8" spans="1:17" ht="27" customHeight="1"/>
     <row r="9" spans="1:17" s="37" customFormat="1" ht="21">
       <c r="B9" s="288" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" s="289"/>
       <c r="D9" s="289"/>
@@ -18632,38 +18629,38 @@
         <v>56</v>
       </c>
       <c r="D11" s="111" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="111" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="111" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="111" t="s">
+      <c r="G11" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="G11" s="111" t="s">
+      <c r="H11" s="320" t="s">
         <v>101</v>
-      </c>
-      <c r="H11" s="320" t="s">
-        <v>102</v>
       </c>
       <c r="I11" s="320"/>
       <c r="J11" s="112" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="112" t="s">
         <v>103</v>
       </c>
-      <c r="K11" s="112" t="s">
+      <c r="L11" s="111" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="111" t="s">
+      <c r="M11" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="M11" s="111" t="s">
+      <c r="N11" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="N11" s="111" t="s">
-        <v>107</v>
-      </c>
       <c r="O11" s="320" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P11" s="320"/>
       <c r="Q11" s="320"/>
@@ -18681,27 +18678,27 @@
         <v/>
       </c>
       <c r="D12" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E12" s="113"/>
       <c r="F12" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H12" s="314"/>
       <c r="I12" s="314"/>
       <c r="J12" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K12" s="115"/>
       <c r="L12" s="114"/>
       <c r="M12" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N12" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O12" s="315"/>
       <c r="P12" s="316"/>
@@ -18720,27 +18717,27 @@
         <v/>
       </c>
       <c r="D13" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E13" s="113"/>
       <c r="F13" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H13" s="314"/>
       <c r="I13" s="314"/>
       <c r="J13" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K13" s="115"/>
       <c r="L13" s="114"/>
       <c r="M13" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N13" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O13" s="315"/>
       <c r="P13" s="316"/>
@@ -18759,27 +18756,27 @@
         <v/>
       </c>
       <c r="D14" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E14" s="113"/>
       <c r="F14" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G14" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H14" s="314"/>
       <c r="I14" s="314"/>
       <c r="J14" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K14" s="115"/>
       <c r="L14" s="114"/>
       <c r="M14" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N14" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O14" s="315"/>
       <c r="P14" s="316"/>
@@ -18798,27 +18795,27 @@
         <v/>
       </c>
       <c r="D15" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15" s="113"/>
       <c r="F15" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G15" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H15" s="314"/>
       <c r="I15" s="314"/>
       <c r="J15" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K15" s="115"/>
       <c r="L15" s="114"/>
       <c r="M15" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N15" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O15" s="315"/>
       <c r="P15" s="316"/>
@@ -18837,27 +18834,27 @@
         <v/>
       </c>
       <c r="D16" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E16" s="113"/>
       <c r="F16" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G16" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H16" s="314"/>
       <c r="I16" s="314"/>
       <c r="J16" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K16" s="115"/>
       <c r="L16" s="114"/>
       <c r="M16" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N16" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O16" s="315"/>
       <c r="P16" s="316"/>
@@ -18876,27 +18873,27 @@
         <v/>
       </c>
       <c r="D17" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E17" s="113"/>
       <c r="F17" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G17" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H17" s="314"/>
       <c r="I17" s="314"/>
       <c r="J17" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K17" s="115"/>
       <c r="L17" s="114"/>
       <c r="M17" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N17" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O17" s="315"/>
       <c r="P17" s="316"/>
@@ -18915,27 +18912,27 @@
         <v/>
       </c>
       <c r="D18" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E18" s="113"/>
       <c r="F18" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H18" s="314"/>
       <c r="I18" s="314"/>
       <c r="J18" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K18" s="115"/>
       <c r="L18" s="114"/>
       <c r="M18" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N18" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O18" s="315"/>
       <c r="P18" s="316"/>
@@ -18954,27 +18951,27 @@
         <v/>
       </c>
       <c r="D19" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E19" s="113"/>
       <c r="F19" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G19" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H19" s="314"/>
       <c r="I19" s="314"/>
       <c r="J19" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K19" s="115"/>
       <c r="L19" s="114"/>
       <c r="M19" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N19" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O19" s="315"/>
       <c r="P19" s="316"/>
@@ -18993,27 +18990,27 @@
         <v/>
       </c>
       <c r="D20" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E20" s="113"/>
       <c r="F20" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G20" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H20" s="314"/>
       <c r="I20" s="314"/>
       <c r="J20" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K20" s="115"/>
       <c r="L20" s="114"/>
       <c r="M20" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N20" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O20" s="315"/>
       <c r="P20" s="316"/>
@@ -19032,27 +19029,27 @@
         <v/>
       </c>
       <c r="D21" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E21" s="113"/>
       <c r="F21" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G21" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H21" s="314"/>
       <c r="I21" s="314"/>
       <c r="J21" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K21" s="115"/>
       <c r="L21" s="114"/>
       <c r="M21" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N21" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O21" s="315"/>
       <c r="P21" s="316"/>
@@ -19071,27 +19068,27 @@
         <v/>
       </c>
       <c r="D22" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E22" s="113"/>
       <c r="F22" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G22" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H22" s="314"/>
       <c r="I22" s="314"/>
       <c r="J22" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K22" s="115"/>
       <c r="L22" s="114"/>
       <c r="M22" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N22" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O22" s="315"/>
       <c r="P22" s="316"/>
@@ -19110,27 +19107,27 @@
         <v/>
       </c>
       <c r="D23" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E23" s="113"/>
       <c r="F23" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G23" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H23" s="314"/>
       <c r="I23" s="314"/>
       <c r="J23" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K23" s="115"/>
       <c r="L23" s="114"/>
       <c r="M23" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N23" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O23" s="315"/>
       <c r="P23" s="316"/>
@@ -19149,27 +19146,27 @@
         <v/>
       </c>
       <c r="D24" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E24" s="113"/>
       <c r="F24" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G24" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H24" s="314"/>
       <c r="I24" s="314"/>
       <c r="J24" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K24" s="115"/>
       <c r="L24" s="114"/>
       <c r="M24" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N24" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O24" s="315"/>
       <c r="P24" s="316"/>
@@ -19188,27 +19185,27 @@
         <v/>
       </c>
       <c r="D25" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" s="113"/>
       <c r="F25" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G25" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H25" s="314"/>
       <c r="I25" s="314"/>
       <c r="J25" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K25" s="115"/>
       <c r="L25" s="114"/>
       <c r="M25" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N25" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O25" s="315"/>
       <c r="P25" s="316"/>
@@ -19227,27 +19224,27 @@
         <v/>
       </c>
       <c r="D26" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" s="113"/>
       <c r="F26" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G26" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H26" s="314"/>
       <c r="I26" s="314"/>
       <c r="J26" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K26" s="115"/>
       <c r="L26" s="114"/>
       <c r="M26" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N26" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O26" s="315"/>
       <c r="P26" s="316"/>
@@ -19266,27 +19263,27 @@
         <v/>
       </c>
       <c r="D27" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E27" s="113"/>
       <c r="F27" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G27" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H27" s="314"/>
       <c r="I27" s="314"/>
       <c r="J27" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K27" s="115"/>
       <c r="L27" s="114"/>
       <c r="M27" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N27" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O27" s="315"/>
       <c r="P27" s="316"/>
@@ -19305,27 +19302,27 @@
         <v/>
       </c>
       <c r="D28" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="113"/>
       <c r="F28" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G28" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H28" s="314"/>
       <c r="I28" s="314"/>
       <c r="J28" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K28" s="115"/>
       <c r="L28" s="114"/>
       <c r="M28" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N28" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O28" s="315"/>
       <c r="P28" s="316"/>
@@ -19344,27 +19341,27 @@
         <v/>
       </c>
       <c r="D29" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" s="113"/>
       <c r="F29" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G29" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H29" s="314"/>
       <c r="I29" s="314"/>
       <c r="J29" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K29" s="115"/>
       <c r="L29" s="114"/>
       <c r="M29" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N29" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O29" s="315"/>
       <c r="P29" s="316"/>
@@ -19383,27 +19380,27 @@
         <v/>
       </c>
       <c r="D30" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="113"/>
       <c r="F30" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H30" s="314"/>
       <c r="I30" s="314"/>
       <c r="J30" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K30" s="115"/>
       <c r="L30" s="114"/>
       <c r="M30" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N30" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O30" s="315"/>
       <c r="P30" s="316"/>
@@ -19422,27 +19419,27 @@
         <v/>
       </c>
       <c r="D31" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="113"/>
       <c r="F31" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G31" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H31" s="314"/>
       <c r="I31" s="314"/>
       <c r="J31" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K31" s="115"/>
       <c r="L31" s="114"/>
       <c r="M31" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N31" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O31" s="315"/>
       <c r="P31" s="316"/>
@@ -19461,27 +19458,27 @@
         <v/>
       </c>
       <c r="D32" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E32" s="113"/>
       <c r="F32" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G32" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H32" s="314"/>
       <c r="I32" s="314"/>
       <c r="J32" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K32" s="115"/>
       <c r="L32" s="114"/>
       <c r="M32" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N32" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O32" s="315"/>
       <c r="P32" s="316"/>
@@ -19500,27 +19497,27 @@
         <v/>
       </c>
       <c r="D33" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="113"/>
       <c r="F33" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G33" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H33" s="314"/>
       <c r="I33" s="314"/>
       <c r="J33" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K33" s="115"/>
       <c r="L33" s="114"/>
       <c r="M33" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N33" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O33" s="315"/>
       <c r="P33" s="316"/>
@@ -19539,27 +19536,27 @@
         <v/>
       </c>
       <c r="D34" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="113"/>
       <c r="F34" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G34" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H34" s="314"/>
       <c r="I34" s="314"/>
       <c r="J34" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K34" s="115"/>
       <c r="L34" s="114"/>
       <c r="M34" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N34" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O34" s="315"/>
       <c r="P34" s="316"/>
@@ -19578,27 +19575,27 @@
         <v/>
       </c>
       <c r="D35" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="113"/>
       <c r="F35" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G35" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H35" s="314"/>
       <c r="I35" s="314"/>
       <c r="J35" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K35" s="115"/>
       <c r="L35" s="114"/>
       <c r="M35" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N35" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O35" s="315"/>
       <c r="P35" s="316"/>
@@ -19617,27 +19614,27 @@
         <v/>
       </c>
       <c r="D36" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="113"/>
       <c r="F36" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G36" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H36" s="314"/>
       <c r="I36" s="314"/>
       <c r="J36" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K36" s="115"/>
       <c r="L36" s="114"/>
       <c r="M36" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N36" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O36" s="315"/>
       <c r="P36" s="316"/>
@@ -19656,27 +19653,27 @@
         <v/>
       </c>
       <c r="D37" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="113"/>
       <c r="F37" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G37" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H37" s="314"/>
       <c r="I37" s="314"/>
       <c r="J37" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K37" s="115"/>
       <c r="L37" s="114"/>
       <c r="M37" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N37" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O37" s="315"/>
       <c r="P37" s="316"/>
@@ -19695,27 +19692,27 @@
         <v/>
       </c>
       <c r="D38" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="113"/>
       <c r="F38" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G38" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H38" s="314"/>
       <c r="I38" s="314"/>
       <c r="J38" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K38" s="115"/>
       <c r="L38" s="114"/>
       <c r="M38" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N38" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O38" s="315"/>
       <c r="P38" s="316"/>
@@ -19734,27 +19731,27 @@
         <v/>
       </c>
       <c r="D39" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="113"/>
       <c r="F39" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G39" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H39" s="314"/>
       <c r="I39" s="314"/>
       <c r="J39" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K39" s="115"/>
       <c r="L39" s="114"/>
       <c r="M39" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N39" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O39" s="315"/>
       <c r="P39" s="316"/>
@@ -19773,27 +19770,27 @@
         <v/>
       </c>
       <c r="D40" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="113"/>
       <c r="F40" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G40" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H40" s="314"/>
       <c r="I40" s="314"/>
       <c r="J40" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K40" s="115"/>
       <c r="L40" s="114"/>
       <c r="M40" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N40" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O40" s="315"/>
       <c r="P40" s="316"/>
@@ -19812,27 +19809,27 @@
         <v/>
       </c>
       <c r="D41" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="113"/>
       <c r="F41" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G41" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H41" s="314"/>
       <c r="I41" s="314"/>
       <c r="J41" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K41" s="115"/>
       <c r="L41" s="114"/>
       <c r="M41" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N41" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O41" s="315"/>
       <c r="P41" s="316"/>
@@ -19851,27 +19848,27 @@
         <v/>
       </c>
       <c r="D42" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="113"/>
       <c r="F42" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G42" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H42" s="314"/>
       <c r="I42" s="314"/>
       <c r="J42" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K42" s="115"/>
       <c r="L42" s="114"/>
       <c r="M42" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N42" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O42" s="315"/>
       <c r="P42" s="316"/>
@@ -19890,27 +19887,27 @@
         <v/>
       </c>
       <c r="D43" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="113"/>
       <c r="F43" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G43" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H43" s="314"/>
       <c r="I43" s="314"/>
       <c r="J43" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K43" s="115"/>
       <c r="L43" s="114"/>
       <c r="M43" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N43" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O43" s="315"/>
       <c r="P43" s="316"/>
@@ -19929,27 +19926,27 @@
         <v/>
       </c>
       <c r="D44" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="113"/>
       <c r="F44" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G44" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H44" s="314"/>
       <c r="I44" s="314"/>
       <c r="J44" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K44" s="115"/>
       <c r="L44" s="114"/>
       <c r="M44" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N44" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O44" s="315"/>
       <c r="P44" s="316"/>
@@ -19968,27 +19965,27 @@
         <v/>
       </c>
       <c r="D45" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="113"/>
       <c r="F45" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G45" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H45" s="314"/>
       <c r="I45" s="314"/>
       <c r="J45" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K45" s="115"/>
       <c r="L45" s="114"/>
       <c r="M45" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N45" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O45" s="315"/>
       <c r="P45" s="316"/>
@@ -20007,27 +20004,27 @@
         <v/>
       </c>
       <c r="D46" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="113"/>
       <c r="F46" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G46" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H46" s="314"/>
       <c r="I46" s="314"/>
       <c r="J46" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K46" s="115"/>
       <c r="L46" s="114"/>
       <c r="M46" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N46" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O46" s="315"/>
       <c r="P46" s="316"/>
@@ -20046,27 +20043,27 @@
         <v/>
       </c>
       <c r="D47" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="113"/>
       <c r="F47" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G47" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H47" s="314"/>
       <c r="I47" s="314"/>
       <c r="J47" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K47" s="115"/>
       <c r="L47" s="114"/>
       <c r="M47" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N47" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O47" s="315"/>
       <c r="P47" s="316"/>
@@ -20085,27 +20082,27 @@
         <v/>
       </c>
       <c r="D48" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="113"/>
       <c r="F48" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G48" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H48" s="314"/>
       <c r="I48" s="314"/>
       <c r="J48" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K48" s="115"/>
       <c r="L48" s="114"/>
       <c r="M48" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N48" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O48" s="315"/>
       <c r="P48" s="316"/>
@@ -20124,27 +20121,27 @@
         <v/>
       </c>
       <c r="D49" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="113"/>
       <c r="F49" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G49" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H49" s="314"/>
       <c r="I49" s="314"/>
       <c r="J49" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K49" s="115"/>
       <c r="L49" s="114"/>
       <c r="M49" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N49" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O49" s="315"/>
       <c r="P49" s="316"/>
@@ -20163,27 +20160,27 @@
         <v/>
       </c>
       <c r="D50" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="113"/>
       <c r="F50" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G50" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H50" s="314"/>
       <c r="I50" s="314"/>
       <c r="J50" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K50" s="120"/>
       <c r="L50" s="114"/>
       <c r="M50" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N50" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O50" s="315"/>
       <c r="P50" s="316"/>
@@ -20202,27 +20199,27 @@
         <v/>
       </c>
       <c r="D51" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="121"/>
       <c r="F51" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G51" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H51" s="309"/>
       <c r="I51" s="309"/>
       <c r="J51" s="123" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K51" s="124"/>
       <c r="L51" s="122"/>
       <c r="M51" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N51" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O51" s="310"/>
       <c r="P51" s="311"/>
@@ -20235,20 +20232,20 @@
       <c r="D52" s="98"/>
       <c r="E52" s="98"/>
       <c r="F52" s="127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G52" s="98"/>
       <c r="H52" s="98"/>
       <c r="I52" s="98"/>
       <c r="J52" s="127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K52" s="98"/>
       <c r="M52" s="127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N52" s="127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O52" s="98"/>
       <c r="P52" s="98"/>
@@ -20257,7 +20254,7 @@
     <row r="53" spans="1:17" ht="27" customHeight="1" thickBot="1"/>
     <row r="54" spans="1:17" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B54" s="248" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="249"/>
       <c r="D54" s="249"/>
@@ -20305,7 +20302,7 @@
       <c r="I56" s="242"/>
       <c r="J56" s="242"/>
       <c r="K56" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L56" s="252"/>
       <c r="M56" s="252"/>
@@ -20435,7 +20432,7 @@
     </row>
     <row r="63" spans="1:17" ht="36.75" customHeight="1">
       <c r="B63" s="308" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C63" s="245"/>
       <c r="D63" s="245"/>
@@ -20774,10 +20771,10 @@
       <c r="H7" s="200"/>
       <c r="I7" s="32"/>
       <c r="J7" s="72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K7" s="202" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L7" s="202"/>
       <c r="M7" s="202"/>
@@ -20796,7 +20793,7 @@
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="J8" s="73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" s="292"/>
       <c r="L8" s="306"/>
@@ -20808,7 +20805,7 @@
     <row r="9" spans="1:17" ht="15" customHeight="1"/>
     <row r="10" spans="1:17" s="37" customFormat="1" ht="30" customHeight="1">
       <c r="B10" s="133" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="134"/>
       <c r="D10" s="134"/>
@@ -20842,30 +20839,30 @@
         <v>56</v>
       </c>
       <c r="D12" s="139" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" s="140"/>
       <c r="F12" s="138" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G12" s="330" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" s="331"/>
       <c r="I12" s="141"/>
       <c r="J12" s="142" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K12" s="332" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L12" s="333"/>
       <c r="M12" s="141"/>
       <c r="N12" s="142" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O12" s="332" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P12" s="333"/>
       <c r="Q12" s="143"/>
@@ -20883,7 +20880,7 @@
         <v/>
       </c>
       <c r="D13" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E13" s="131"/>
       <c r="F13" s="145"/>
@@ -20895,7 +20892,7 @@
       <c r="L13" s="317"/>
       <c r="M13" s="146"/>
       <c r="N13" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O13" s="316"/>
       <c r="P13" s="317"/>
@@ -20914,7 +20911,7 @@
         <v/>
       </c>
       <c r="D14" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E14" s="131"/>
       <c r="F14" s="116"/>
@@ -20926,7 +20923,7 @@
       <c r="L14" s="317"/>
       <c r="M14" s="146"/>
       <c r="N14" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O14" s="316"/>
       <c r="P14" s="317"/>
@@ -20945,7 +20942,7 @@
         <v/>
       </c>
       <c r="D15" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15" s="131"/>
       <c r="F15" s="116"/>
@@ -20957,7 +20954,7 @@
       <c r="L15" s="317"/>
       <c r="M15" s="146"/>
       <c r="N15" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O15" s="316"/>
       <c r="P15" s="317"/>
@@ -20976,7 +20973,7 @@
         <v/>
       </c>
       <c r="D16" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E16" s="131"/>
       <c r="F16" s="116"/>
@@ -20988,7 +20985,7 @@
       <c r="L16" s="317"/>
       <c r="M16" s="146"/>
       <c r="N16" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O16" s="316"/>
       <c r="P16" s="317"/>
@@ -21007,7 +21004,7 @@
         <v/>
       </c>
       <c r="D17" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E17" s="131"/>
       <c r="F17" s="116"/>
@@ -21019,7 +21016,7 @@
       <c r="L17" s="317"/>
       <c r="M17" s="146"/>
       <c r="N17" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O17" s="316"/>
       <c r="P17" s="317"/>
@@ -21037,7 +21034,7 @@
         <v/>
       </c>
       <c r="D18" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E18" s="131"/>
       <c r="F18" s="116"/>
@@ -21049,7 +21046,7 @@
       <c r="L18" s="317"/>
       <c r="M18" s="146"/>
       <c r="N18" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O18" s="316"/>
       <c r="P18" s="317"/>
@@ -21067,7 +21064,7 @@
         <v/>
       </c>
       <c r="D19" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E19" s="131"/>
       <c r="F19" s="116"/>
@@ -21079,7 +21076,7 @@
       <c r="L19" s="317"/>
       <c r="M19" s="146"/>
       <c r="N19" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O19" s="316"/>
       <c r="P19" s="317"/>
@@ -21097,7 +21094,7 @@
         <v/>
       </c>
       <c r="D20" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E20" s="131"/>
       <c r="F20" s="116"/>
@@ -21109,7 +21106,7 @@
       <c r="L20" s="317"/>
       <c r="M20" s="146"/>
       <c r="N20" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O20" s="316"/>
       <c r="P20" s="317"/>
@@ -21127,7 +21124,7 @@
         <v/>
       </c>
       <c r="D21" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E21" s="131"/>
       <c r="F21" s="116"/>
@@ -21139,7 +21136,7 @@
       <c r="L21" s="317"/>
       <c r="M21" s="146"/>
       <c r="N21" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O21" s="316"/>
       <c r="P21" s="317"/>
@@ -21157,7 +21154,7 @@
         <v/>
       </c>
       <c r="D22" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E22" s="131"/>
       <c r="F22" s="116"/>
@@ -21169,7 +21166,7 @@
       <c r="L22" s="317"/>
       <c r="M22" s="146"/>
       <c r="N22" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O22" s="316"/>
       <c r="P22" s="317"/>
@@ -21187,7 +21184,7 @@
         <v/>
       </c>
       <c r="D23" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E23" s="131"/>
       <c r="F23" s="116"/>
@@ -21199,7 +21196,7 @@
       <c r="L23" s="317"/>
       <c r="M23" s="146"/>
       <c r="N23" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O23" s="316"/>
       <c r="P23" s="317"/>
@@ -21217,7 +21214,7 @@
         <v/>
       </c>
       <c r="D24" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E24" s="131"/>
       <c r="F24" s="116"/>
@@ -21229,7 +21226,7 @@
       <c r="L24" s="317"/>
       <c r="M24" s="146"/>
       <c r="N24" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O24" s="316"/>
       <c r="P24" s="317"/>
@@ -21247,7 +21244,7 @@
         <v/>
       </c>
       <c r="D25" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" s="131"/>
       <c r="F25" s="116"/>
@@ -21259,7 +21256,7 @@
       <c r="L25" s="317"/>
       <c r="M25" s="146"/>
       <c r="N25" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O25" s="316"/>
       <c r="P25" s="317"/>
@@ -21277,7 +21274,7 @@
         <v/>
       </c>
       <c r="D26" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" s="131"/>
       <c r="F26" s="116"/>
@@ -21289,7 +21286,7 @@
       <c r="L26" s="317"/>
       <c r="M26" s="146"/>
       <c r="N26" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O26" s="316"/>
       <c r="P26" s="317"/>
@@ -21307,7 +21304,7 @@
         <v/>
       </c>
       <c r="D27" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E27" s="131"/>
       <c r="F27" s="116"/>
@@ -21319,7 +21316,7 @@
       <c r="L27" s="317"/>
       <c r="M27" s="146"/>
       <c r="N27" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O27" s="316"/>
       <c r="P27" s="317"/>
@@ -21337,7 +21334,7 @@
         <v/>
       </c>
       <c r="D28" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="131"/>
       <c r="F28" s="116"/>
@@ -21349,7 +21346,7 @@
       <c r="L28" s="317"/>
       <c r="M28" s="146"/>
       <c r="N28" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O28" s="316"/>
       <c r="P28" s="317"/>
@@ -21367,7 +21364,7 @@
         <v/>
       </c>
       <c r="D29" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" s="131"/>
       <c r="F29" s="116"/>
@@ -21379,7 +21376,7 @@
       <c r="L29" s="317"/>
       <c r="M29" s="146"/>
       <c r="N29" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O29" s="316"/>
       <c r="P29" s="317"/>
@@ -21397,7 +21394,7 @@
         <v/>
       </c>
       <c r="D30" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="131"/>
       <c r="F30" s="116"/>
@@ -21409,7 +21406,7 @@
       <c r="L30" s="317"/>
       <c r="M30" s="146"/>
       <c r="N30" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O30" s="316"/>
       <c r="P30" s="317"/>
@@ -21427,7 +21424,7 @@
         <v/>
       </c>
       <c r="D31" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="131"/>
       <c r="F31" s="116"/>
@@ -21439,7 +21436,7 @@
       <c r="L31" s="317"/>
       <c r="M31" s="146"/>
       <c r="N31" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O31" s="316"/>
       <c r="P31" s="317"/>
@@ -21457,7 +21454,7 @@
         <v/>
       </c>
       <c r="D32" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E32" s="131"/>
       <c r="F32" s="116"/>
@@ -21469,7 +21466,7 @@
       <c r="L32" s="317"/>
       <c r="M32" s="146"/>
       <c r="N32" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O32" s="316"/>
       <c r="P32" s="317"/>
@@ -21487,7 +21484,7 @@
         <v/>
       </c>
       <c r="D33" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="131"/>
       <c r="F33" s="116"/>
@@ -21499,7 +21496,7 @@
       <c r="L33" s="317"/>
       <c r="M33" s="146"/>
       <c r="N33" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O33" s="316"/>
       <c r="P33" s="317"/>
@@ -21517,7 +21514,7 @@
         <v/>
       </c>
       <c r="D34" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="131"/>
       <c r="F34" s="116"/>
@@ -21529,7 +21526,7 @@
       <c r="L34" s="317"/>
       <c r="M34" s="146"/>
       <c r="N34" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O34" s="316"/>
       <c r="P34" s="317"/>
@@ -21547,7 +21544,7 @@
         <v/>
       </c>
       <c r="D35" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="131"/>
       <c r="F35" s="116"/>
@@ -21559,7 +21556,7 @@
       <c r="L35" s="317"/>
       <c r="M35" s="146"/>
       <c r="N35" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O35" s="316"/>
       <c r="P35" s="317"/>
@@ -21577,7 +21574,7 @@
         <v/>
       </c>
       <c r="D36" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="131"/>
       <c r="F36" s="116"/>
@@ -21589,7 +21586,7 @@
       <c r="L36" s="317"/>
       <c r="M36" s="146"/>
       <c r="N36" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O36" s="316"/>
       <c r="P36" s="317"/>
@@ -21607,7 +21604,7 @@
         <v/>
       </c>
       <c r="D37" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="131"/>
       <c r="F37" s="116"/>
@@ -21619,7 +21616,7 @@
       <c r="L37" s="317"/>
       <c r="M37" s="146"/>
       <c r="N37" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O37" s="316"/>
       <c r="P37" s="317"/>
@@ -21637,7 +21634,7 @@
         <v/>
       </c>
       <c r="D38" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="131"/>
       <c r="F38" s="116"/>
@@ -21649,7 +21646,7 @@
       <c r="L38" s="317"/>
       <c r="M38" s="146"/>
       <c r="N38" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O38" s="316"/>
       <c r="P38" s="317"/>
@@ -21667,7 +21664,7 @@
         <v/>
       </c>
       <c r="D39" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="131"/>
       <c r="F39" s="116"/>
@@ -21679,7 +21676,7 @@
       <c r="L39" s="317"/>
       <c r="M39" s="146"/>
       <c r="N39" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O39" s="316"/>
       <c r="P39" s="317"/>
@@ -21697,7 +21694,7 @@
         <v/>
       </c>
       <c r="D40" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="131"/>
       <c r="F40" s="116"/>
@@ -21709,7 +21706,7 @@
       <c r="L40" s="317"/>
       <c r="M40" s="146"/>
       <c r="N40" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O40" s="316"/>
       <c r="P40" s="317"/>
@@ -21727,7 +21724,7 @@
         <v/>
       </c>
       <c r="D41" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="131"/>
       <c r="F41" s="116"/>
@@ -21739,7 +21736,7 @@
       <c r="L41" s="317"/>
       <c r="M41" s="146"/>
       <c r="N41" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O41" s="316"/>
       <c r="P41" s="317"/>
@@ -21757,7 +21754,7 @@
         <v/>
       </c>
       <c r="D42" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="131"/>
       <c r="F42" s="116"/>
@@ -21769,7 +21766,7 @@
       <c r="L42" s="317"/>
       <c r="M42" s="146"/>
       <c r="N42" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O42" s="316"/>
       <c r="P42" s="317"/>
@@ -21787,7 +21784,7 @@
         <v/>
       </c>
       <c r="D43" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="131"/>
       <c r="F43" s="116"/>
@@ -21799,7 +21796,7 @@
       <c r="L43" s="118"/>
       <c r="M43" s="146"/>
       <c r="N43" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O43" s="117"/>
       <c r="P43" s="118"/>
@@ -21817,7 +21814,7 @@
         <v/>
       </c>
       <c r="D44" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="131"/>
       <c r="F44" s="116"/>
@@ -21829,7 +21826,7 @@
       <c r="L44" s="118"/>
       <c r="M44" s="146"/>
       <c r="N44" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O44" s="117"/>
       <c r="P44" s="118"/>
@@ -21847,7 +21844,7 @@
         <v/>
       </c>
       <c r="D45" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="131"/>
       <c r="F45" s="116"/>
@@ -21859,7 +21856,7 @@
       <c r="L45" s="118"/>
       <c r="M45" s="146"/>
       <c r="N45" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O45" s="117"/>
       <c r="P45" s="118"/>
@@ -21877,7 +21874,7 @@
         <v/>
       </c>
       <c r="D46" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="131"/>
       <c r="F46" s="116"/>
@@ -21889,7 +21886,7 @@
       <c r="L46" s="118"/>
       <c r="M46" s="146"/>
       <c r="N46" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O46" s="117"/>
       <c r="P46" s="118"/>
@@ -21907,7 +21904,7 @@
         <v/>
       </c>
       <c r="D47" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="131"/>
       <c r="F47" s="116"/>
@@ -21919,7 +21916,7 @@
       <c r="L47" s="118"/>
       <c r="M47" s="146"/>
       <c r="N47" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O47" s="117"/>
       <c r="P47" s="118"/>
@@ -21937,7 +21934,7 @@
         <v/>
       </c>
       <c r="D48" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="131"/>
       <c r="F48" s="116"/>
@@ -21949,7 +21946,7 @@
       <c r="L48" s="317"/>
       <c r="M48" s="146"/>
       <c r="N48" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O48" s="316"/>
       <c r="P48" s="317"/>
@@ -21967,7 +21964,7 @@
         <v/>
       </c>
       <c r="D49" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="131"/>
       <c r="F49" s="116"/>
@@ -21979,7 +21976,7 @@
       <c r="L49" s="317"/>
       <c r="M49" s="146"/>
       <c r="N49" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O49" s="316"/>
       <c r="P49" s="317"/>
@@ -21997,7 +21994,7 @@
         <v/>
       </c>
       <c r="D50" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="131"/>
       <c r="F50" s="116"/>
@@ -22009,7 +22006,7 @@
       <c r="L50" s="317"/>
       <c r="M50" s="146"/>
       <c r="N50" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O50" s="316"/>
       <c r="P50" s="317"/>
@@ -22027,7 +22024,7 @@
         <v/>
       </c>
       <c r="D51" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="131"/>
       <c r="F51" s="116"/>
@@ -22039,7 +22036,7 @@
       <c r="L51" s="317"/>
       <c r="M51" s="146"/>
       <c r="N51" s="147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O51" s="316"/>
       <c r="P51" s="317"/>
@@ -22057,7 +22054,7 @@
         <v/>
       </c>
       <c r="D52" s="144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="131"/>
       <c r="F52" s="125"/>
@@ -22069,7 +22066,7 @@
       <c r="L52" s="312"/>
       <c r="M52" s="146"/>
       <c r="N52" s="149" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O52" s="311"/>
       <c r="P52" s="312"/>
@@ -22077,7 +22074,7 @@
     <row r="53" spans="1:16" ht="27" customHeight="1"/>
     <row r="54" spans="1:16" ht="40.5" customHeight="1">
       <c r="B54" s="288" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="289"/>
       <c r="D54" s="289"/>
@@ -22108,7 +22105,7 @@
       <c r="I55" s="313"/>
       <c r="J55" s="313"/>
       <c r="K55" s="324" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L55" s="325"/>
       <c r="M55" s="325"/>
@@ -22238,7 +22235,7 @@
     </row>
     <row r="62" spans="1:16" ht="36.75" customHeight="1">
       <c r="B62" s="308" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C62" s="245"/>
       <c r="D62" s="245"/>
@@ -22555,7 +22552,7 @@
         <v>27</v>
       </c>
       <c r="J6" s="202" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K6" s="202"/>
       <c r="L6" s="202"/>
@@ -22570,7 +22567,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="292"/>
       <c r="K7" s="306"/>
@@ -22626,7 +22623,7 @@
       <c r="L12" s="271"/>
       <c r="M12" s="272"/>
       <c r="N12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="27" customHeight="1"/>
@@ -22663,7 +22660,7 @@
     <row r="16" spans="2:14" ht="27" customHeight="1"/>
     <row r="17" spans="2:14">
       <c r="B17" s="350" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="350"/>
       <c r="D17" s="350"/>
@@ -22731,7 +22728,7 @@
     <row r="23" spans="2:14" ht="27" customHeight="1"/>
     <row r="24" spans="2:14" s="37" customFormat="1" ht="21">
       <c r="B24" s="199" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="199"/>
       <c r="D24" s="199"/>
@@ -22748,7 +22745,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L25" s="75"/>
       <c r="M25" s="75"/>
@@ -22756,22 +22753,22 @@
     </row>
     <row r="26" spans="2:14" ht="21" customHeight="1">
       <c r="D26" s="151" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F26" s="152"/>
       <c r="L26" s="151" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M26" s="151" t="s">
         <v>40</v>
       </c>
       <c r="N26" s="151" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="2:14" ht="21" customHeight="1">
       <c r="C27" s="94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" s="54">
         <f>COUNTIFS($C$39:$C$78,"&lt;&gt;",$D$39:$D$78,"&lt;&gt;Baixa")-COUNTBLANK($C$39:$C$78)</f>
@@ -22781,7 +22778,7 @@
         <v>40</v>
       </c>
       <c r="G27" s="342" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H27" s="342"/>
       <c r="I27" s="342"/>
@@ -22813,7 +22810,7 @@
       </c>
       <c r="F28" s="154"/>
       <c r="G28" s="342" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H28" s="342"/>
       <c r="I28" s="342"/>
@@ -22833,7 +22830,7 @@
     </row>
     <row r="29" spans="2:14" ht="21" customHeight="1">
       <c r="C29" s="94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" s="56">
         <v>0</v>
@@ -22843,7 +22840,7 @@
         <v>-</v>
       </c>
       <c r="G29" s="342" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H29" s="342"/>
       <c r="I29" s="342"/>
@@ -22863,7 +22860,7 @@
     </row>
     <row r="30" spans="2:14" ht="21" customHeight="1">
       <c r="C30" s="94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" s="56">
         <v>0</v>
@@ -22873,7 +22870,7 @@
         <v>-</v>
       </c>
       <c r="G30" s="342" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H30" s="342"/>
       <c r="I30" s="342"/>
@@ -22893,7 +22890,7 @@
     </row>
     <row r="31" spans="2:14" ht="21" customHeight="1">
       <c r="C31" s="94" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D31" s="56">
         <v>0</v>
@@ -22903,7 +22900,7 @@
         <v>-</v>
       </c>
       <c r="G31" s="342" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H31" s="342"/>
       <c r="I31" s="342"/>
@@ -22923,7 +22920,7 @@
     </row>
     <row r="32" spans="2:14" ht="21" customHeight="1" thickBot="1">
       <c r="C32" s="94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" s="155">
         <v>0</v>
@@ -22944,7 +22941,7 @@
       <c r="E33" s="40"/>
       <c r="F33" s="40"/>
       <c r="G33" s="342" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H33" s="342"/>
       <c r="I33" s="342"/>
@@ -22968,7 +22965,7 @@
       <c r="E34" s="40"/>
       <c r="F34" s="40"/>
       <c r="G34" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H34" s="342"/>
       <c r="I34" s="342"/>
@@ -23014,26 +23011,26 @@
         <v>56</v>
       </c>
       <c r="D38" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E38" s="160" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" s="343" t="s">
         <v>125</v>
-      </c>
-      <c r="F38" s="343" t="s">
-        <v>126</v>
       </c>
       <c r="G38" s="343"/>
       <c r="H38" s="160" t="s">
+        <v>126</v>
+      </c>
+      <c r="I38" s="160" t="s">
         <v>127</v>
       </c>
-      <c r="I38" s="160" t="s">
+      <c r="J38" s="161" t="s">
         <v>128</v>
       </c>
-      <c r="J38" s="161" t="s">
+      <c r="K38" s="344" t="s">
         <v>129</v>
-      </c>
-      <c r="K38" s="344" t="s">
-        <v>130</v>
       </c>
       <c r="L38" s="344"/>
       <c r="M38" s="344"/>
@@ -23052,19 +23049,19 @@
         <v/>
       </c>
       <c r="D39" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F39" s="346"/>
       <c r="G39" s="346"/>
       <c r="H39" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I39" s="165"/>
       <c r="J39" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K39" s="347"/>
       <c r="L39" s="348"/>
@@ -23084,19 +23081,19 @@
         <v/>
       </c>
       <c r="D40" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F40" s="338"/>
       <c r="G40" s="338"/>
       <c r="H40" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I40" s="166"/>
       <c r="J40" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K40" s="339"/>
       <c r="L40" s="340"/>
@@ -23116,19 +23113,19 @@
         <v/>
       </c>
       <c r="D41" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F41" s="338"/>
       <c r="G41" s="338"/>
       <c r="H41" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I41" s="166"/>
       <c r="J41" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K41" s="339"/>
       <c r="L41" s="340"/>
@@ -23148,19 +23145,19 @@
         <v/>
       </c>
       <c r="D42" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F42" s="338"/>
       <c r="G42" s="338"/>
       <c r="H42" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I42" s="166"/>
       <c r="J42" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K42" s="339"/>
       <c r="L42" s="340"/>
@@ -23180,19 +23177,19 @@
         <v/>
       </c>
       <c r="D43" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F43" s="338"/>
       <c r="G43" s="338"/>
       <c r="H43" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I43" s="166"/>
       <c r="J43" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K43" s="339"/>
       <c r="L43" s="340"/>
@@ -23212,19 +23209,19 @@
         <v/>
       </c>
       <c r="D44" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F44" s="338"/>
       <c r="G44" s="338"/>
       <c r="H44" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I44" s="166"/>
       <c r="J44" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K44" s="339"/>
       <c r="L44" s="340"/>
@@ -23244,19 +23241,19 @@
         <v/>
       </c>
       <c r="D45" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F45" s="338"/>
       <c r="G45" s="338"/>
       <c r="H45" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I45" s="166"/>
       <c r="J45" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K45" s="339"/>
       <c r="L45" s="340"/>
@@ -23276,19 +23273,19 @@
         <v/>
       </c>
       <c r="D46" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F46" s="338"/>
       <c r="G46" s="338"/>
       <c r="H46" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I46" s="166"/>
       <c r="J46" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K46" s="339"/>
       <c r="L46" s="340"/>
@@ -23308,19 +23305,19 @@
         <v/>
       </c>
       <c r="D47" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F47" s="338"/>
       <c r="G47" s="338"/>
       <c r="H47" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I47" s="166"/>
       <c r="J47" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K47" s="339"/>
       <c r="L47" s="340"/>
@@ -23340,19 +23337,19 @@
         <v/>
       </c>
       <c r="D48" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F48" s="338"/>
       <c r="G48" s="338"/>
       <c r="H48" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I48" s="166"/>
       <c r="J48" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K48" s="339"/>
       <c r="L48" s="340"/>
@@ -23372,19 +23369,19 @@
         <v/>
       </c>
       <c r="D49" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F49" s="338"/>
       <c r="G49" s="338"/>
       <c r="H49" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I49" s="166"/>
       <c r="J49" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K49" s="339"/>
       <c r="L49" s="340"/>
@@ -23404,19 +23401,19 @@
         <v/>
       </c>
       <c r="D50" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F50" s="338"/>
       <c r="G50" s="338"/>
       <c r="H50" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I50" s="166"/>
       <c r="J50" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K50" s="339"/>
       <c r="L50" s="340"/>
@@ -23436,19 +23433,19 @@
         <v/>
       </c>
       <c r="D51" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F51" s="338"/>
       <c r="G51" s="338"/>
       <c r="H51" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I51" s="166"/>
       <c r="J51" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K51" s="339"/>
       <c r="L51" s="340"/>
@@ -23468,19 +23465,19 @@
         <v/>
       </c>
       <c r="D52" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F52" s="338"/>
       <c r="G52" s="338"/>
       <c r="H52" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I52" s="166"/>
       <c r="J52" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K52" s="339"/>
       <c r="L52" s="340"/>
@@ -23500,19 +23497,19 @@
         <v/>
       </c>
       <c r="D53" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F53" s="338"/>
       <c r="G53" s="338"/>
       <c r="H53" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I53" s="166"/>
       <c r="J53" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K53" s="339"/>
       <c r="L53" s="340"/>
@@ -23532,19 +23529,19 @@
         <v/>
       </c>
       <c r="D54" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F54" s="338"/>
       <c r="G54" s="338"/>
       <c r="H54" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I54" s="166"/>
       <c r="J54" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K54" s="339"/>
       <c r="L54" s="340"/>
@@ -23564,19 +23561,19 @@
         <v/>
       </c>
       <c r="D55" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F55" s="338"/>
       <c r="G55" s="338"/>
       <c r="H55" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I55" s="166"/>
       <c r="J55" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K55" s="339"/>
       <c r="L55" s="340"/>
@@ -23596,19 +23593,19 @@
         <v/>
       </c>
       <c r="D56" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F56" s="338"/>
       <c r="G56" s="338"/>
       <c r="H56" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I56" s="166"/>
       <c r="J56" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K56" s="339"/>
       <c r="L56" s="340"/>
@@ -23628,19 +23625,19 @@
         <v/>
       </c>
       <c r="D57" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F57" s="338"/>
       <c r="G57" s="338"/>
       <c r="H57" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I57" s="166"/>
       <c r="J57" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K57" s="339"/>
       <c r="L57" s="340"/>
@@ -23660,19 +23657,19 @@
         <v/>
       </c>
       <c r="D58" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F58" s="338"/>
       <c r="G58" s="338"/>
       <c r="H58" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I58" s="166"/>
       <c r="J58" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K58" s="339"/>
       <c r="L58" s="340"/>
@@ -23692,19 +23689,19 @@
         <v/>
       </c>
       <c r="D59" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F59" s="338"/>
       <c r="G59" s="338"/>
       <c r="H59" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I59" s="166"/>
       <c r="J59" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K59" s="339"/>
       <c r="L59" s="340"/>
@@ -23724,19 +23721,19 @@
         <v/>
       </c>
       <c r="D60" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F60" s="338"/>
       <c r="G60" s="338"/>
       <c r="H60" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I60" s="166"/>
       <c r="J60" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K60" s="339"/>
       <c r="L60" s="340"/>
@@ -23756,19 +23753,19 @@
         <v/>
       </c>
       <c r="D61" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F61" s="338"/>
       <c r="G61" s="338"/>
       <c r="H61" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I61" s="166"/>
       <c r="J61" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K61" s="339"/>
       <c r="L61" s="340"/>
@@ -23788,19 +23785,19 @@
         <v/>
       </c>
       <c r="D62" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F62" s="338"/>
       <c r="G62" s="338"/>
       <c r="H62" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I62" s="166"/>
       <c r="J62" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K62" s="339"/>
       <c r="L62" s="340"/>
@@ -23820,19 +23817,19 @@
         <v/>
       </c>
       <c r="D63" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F63" s="338"/>
       <c r="G63" s="338"/>
       <c r="H63" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I63" s="166"/>
       <c r="J63" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K63" s="339"/>
       <c r="L63" s="340"/>
@@ -23852,19 +23849,19 @@
         <v/>
       </c>
       <c r="D64" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E64" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F64" s="338"/>
       <c r="G64" s="338"/>
       <c r="H64" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I64" s="166"/>
       <c r="J64" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K64" s="339"/>
       <c r="L64" s="340"/>
@@ -23884,19 +23881,19 @@
         <v/>
       </c>
       <c r="D65" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F65" s="338"/>
       <c r="G65" s="338"/>
       <c r="H65" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I65" s="166"/>
       <c r="J65" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K65" s="339"/>
       <c r="L65" s="340"/>
@@ -23916,19 +23913,19 @@
         <v/>
       </c>
       <c r="D66" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F66" s="338"/>
       <c r="G66" s="338"/>
       <c r="H66" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I66" s="166"/>
       <c r="J66" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K66" s="339"/>
       <c r="L66" s="340"/>
@@ -23948,19 +23945,19 @@
         <v/>
       </c>
       <c r="D67" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F67" s="338"/>
       <c r="G67" s="338"/>
       <c r="H67" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I67" s="166"/>
       <c r="J67" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K67" s="339"/>
       <c r="L67" s="340"/>
@@ -23980,19 +23977,19 @@
         <v/>
       </c>
       <c r="D68" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E68" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F68" s="338"/>
       <c r="G68" s="338"/>
       <c r="H68" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I68" s="166"/>
       <c r="J68" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K68" s="339"/>
       <c r="L68" s="340"/>
@@ -24012,19 +24009,19 @@
         <v/>
       </c>
       <c r="D69" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E69" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F69" s="338"/>
       <c r="G69" s="338"/>
       <c r="H69" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I69" s="166"/>
       <c r="J69" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K69" s="339"/>
       <c r="L69" s="340"/>
@@ -24044,19 +24041,19 @@
         <v/>
       </c>
       <c r="D70" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E70" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F70" s="338"/>
       <c r="G70" s="338"/>
       <c r="H70" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I70" s="166"/>
       <c r="J70" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K70" s="339"/>
       <c r="L70" s="340"/>
@@ -24076,19 +24073,19 @@
         <v/>
       </c>
       <c r="D71" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E71" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F71" s="338"/>
       <c r="G71" s="338"/>
       <c r="H71" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I71" s="166"/>
       <c r="J71" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K71" s="339"/>
       <c r="L71" s="340"/>
@@ -24108,19 +24105,19 @@
         <v/>
       </c>
       <c r="D72" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E72" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F72" s="338"/>
       <c r="G72" s="338"/>
       <c r="H72" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I72" s="166"/>
       <c r="J72" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K72" s="339"/>
       <c r="L72" s="340"/>
@@ -24140,19 +24137,19 @@
         <v/>
       </c>
       <c r="D73" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E73" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F73" s="338"/>
       <c r="G73" s="338"/>
       <c r="H73" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I73" s="166"/>
       <c r="J73" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K73" s="339"/>
       <c r="L73" s="340"/>
@@ -24172,19 +24169,19 @@
         <v/>
       </c>
       <c r="D74" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E74" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F74" s="338"/>
       <c r="G74" s="338"/>
       <c r="H74" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I74" s="166"/>
       <c r="J74" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K74" s="339"/>
       <c r="L74" s="340"/>
@@ -24204,19 +24201,19 @@
         <v/>
       </c>
       <c r="D75" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E75" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F75" s="338"/>
       <c r="G75" s="338"/>
       <c r="H75" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I75" s="166"/>
       <c r="J75" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K75" s="339"/>
       <c r="L75" s="340"/>
@@ -24236,19 +24233,19 @@
         <v/>
       </c>
       <c r="D76" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E76" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F76" s="338"/>
       <c r="G76" s="338"/>
       <c r="H76" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I76" s="166"/>
       <c r="J76" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K76" s="339"/>
       <c r="L76" s="340"/>
@@ -24268,19 +24265,19 @@
         <v/>
       </c>
       <c r="D77" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E77" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F77" s="338"/>
       <c r="G77" s="338"/>
       <c r="H77" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I77" s="166"/>
       <c r="J77" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K77" s="339"/>
       <c r="L77" s="340"/>
@@ -24300,19 +24297,19 @@
         <v/>
       </c>
       <c r="D78" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E78" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F78" s="338"/>
       <c r="G78" s="338"/>
       <c r="H78" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I78" s="166"/>
       <c r="J78" s="164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K78" s="339"/>
       <c r="L78" s="340"/>
@@ -24322,7 +24319,7 @@
     <row r="79" spans="1:14" ht="16.149999999999999" thickBot="1"/>
     <row r="80" spans="1:14" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B80" s="248" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C80" s="249"/>
       <c r="D80" s="249"/>
@@ -24347,10 +24344,10 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="K81" s="293" t="s">
         <v>83</v>
-      </c>
-      <c r="K81" s="293" t="s">
-        <v>84</v>
       </c>
       <c r="L81" s="293"/>
       <c r="M81" s="293"/>
@@ -24513,7 +24510,7 @@
     </row>
     <row r="90" spans="1:14" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B90" s="248" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C90" s="249"/>
       <c r="D90" s="249"/>
@@ -24556,7 +24553,7 @@
       <c r="H92" s="242"/>
       <c r="I92" s="242"/>
       <c r="J92" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K92" s="252"/>
       <c r="L92" s="252"/>
@@ -24673,7 +24670,7 @@
     </row>
     <row r="99" spans="1:14" ht="50.25" customHeight="1">
       <c r="B99" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C99" s="243"/>
       <c r="D99" s="243"/>
@@ -25022,7 +25019,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="292"/>
       <c r="K7" s="306"/>
@@ -25032,7 +25029,7 @@
     <row r="8" spans="2:14" ht="27" customHeight="1"/>
     <row r="9" spans="2:14" s="37" customFormat="1" ht="21">
       <c r="B9" s="199" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="199"/>
       <c r="D9" s="199"/>
@@ -25049,37 +25046,37 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" s="74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="19.5" customHeight="1">
       <c r="D11" s="151" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F11" s="152"/>
       <c r="L11" s="151" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M11" s="151" t="s">
         <v>40</v>
       </c>
       <c r="N11" s="151" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="19.5" customHeight="1">
       <c r="C12" s="94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="54">
         <f>COUNTIFS($C$24:$C$63,"&lt;&gt;",$D$24:$D$63,"&lt;&gt;Baixa")-COUNTBLANK($C$24:$C$63)</f>
         <v>0</v>
       </c>
       <c r="E12" s="169" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="342" t="s">
         <v>132</v>
-      </c>
-      <c r="G12" s="342" t="s">
-        <v>133</v>
       </c>
       <c r="H12" s="342"/>
       <c r="I12" s="342"/>
@@ -25122,7 +25119,7 @@
     </row>
     <row r="14" spans="2:14" ht="19.5" customHeight="1">
       <c r="C14" s="173" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D14" s="54">
         <f>COUNTIFS(FINAL!$C$39:$C$78,"&lt;&gt;",FINAL!$D$39:$D$78,"&lt;&gt;Baixa",FINAL!$H$39:$H$78,"Sí")</f>
@@ -25133,7 +25130,7 @@
         <v>-</v>
       </c>
       <c r="G14" s="342" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H14" s="342"/>
       <c r="I14" s="342"/>
@@ -25154,7 +25151,7 @@
     </row>
     <row r="15" spans="2:14" ht="19.5" customHeight="1" thickBot="1">
       <c r="C15" s="77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" s="56">
         <v>0</v>
@@ -25164,7 +25161,7 @@
         <v>-</v>
       </c>
       <c r="G15" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H15" s="342"/>
       <c r="I15" s="342"/>
@@ -25185,7 +25182,7 @@
     </row>
     <row r="16" spans="2:14" ht="19.5" customHeight="1">
       <c r="C16" s="77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D16" s="56">
         <v>0</v>
@@ -25205,7 +25202,7 @@
     </row>
     <row r="17" spans="1:14" ht="19.5" customHeight="1" thickBot="1">
       <c r="B17" s="342" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="342"/>
       <c r="D17" s="59">
@@ -25235,7 +25232,7 @@
     <row r="20" spans="1:14"/>
     <row r="21" spans="1:14" s="37" customFormat="1" ht="21">
       <c r="B21" s="199" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="199"/>
       <c r="D21" s="199"/>
@@ -25259,18 +25256,18 @@
         <v>56</v>
       </c>
       <c r="D23" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E23" s="359" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F23" s="359"/>
       <c r="G23" s="359" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H23" s="359"/>
       <c r="I23" s="359" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J23" s="359"/>
       <c r="K23" s="359"/>
@@ -25291,14 +25288,14 @@
         <v/>
       </c>
       <c r="D24" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E24" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F24" s="346"/>
       <c r="G24" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H24" s="349"/>
       <c r="I24" s="356"/>
@@ -25321,14 +25318,14 @@
         <v/>
       </c>
       <c r="D25" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F25" s="346"/>
       <c r="G25" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H25" s="349"/>
       <c r="I25" s="353"/>
@@ -25351,14 +25348,14 @@
         <v/>
       </c>
       <c r="D26" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="346"/>
       <c r="G26" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H26" s="349"/>
       <c r="I26" s="353"/>
@@ -25381,14 +25378,14 @@
         <v/>
       </c>
       <c r="D27" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E27" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="346"/>
       <c r="G27" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H27" s="349"/>
       <c r="I27" s="353"/>
@@ -25411,14 +25408,14 @@
         <v/>
       </c>
       <c r="D28" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F28" s="346"/>
       <c r="G28" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H28" s="349"/>
       <c r="I28" s="353"/>
@@ -25441,14 +25438,14 @@
         <v/>
       </c>
       <c r="D29" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F29" s="346"/>
       <c r="G29" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H29" s="349"/>
       <c r="I29" s="353"/>
@@ -25471,14 +25468,14 @@
         <v/>
       </c>
       <c r="D30" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F30" s="346"/>
       <c r="G30" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H30" s="349"/>
       <c r="I30" s="353"/>
@@ -25501,14 +25498,14 @@
         <v/>
       </c>
       <c r="D31" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F31" s="346"/>
       <c r="G31" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H31" s="349"/>
       <c r="I31" s="353"/>
@@ -25531,14 +25528,14 @@
         <v/>
       </c>
       <c r="D32" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E32" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F32" s="346"/>
       <c r="G32" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H32" s="349"/>
       <c r="I32" s="353"/>
@@ -25561,14 +25558,14 @@
         <v/>
       </c>
       <c r="D33" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F33" s="346"/>
       <c r="G33" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H33" s="349"/>
       <c r="I33" s="353"/>
@@ -25591,14 +25588,14 @@
         <v/>
       </c>
       <c r="D34" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F34" s="346"/>
       <c r="G34" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H34" s="349"/>
       <c r="I34" s="353"/>
@@ -25621,14 +25618,14 @@
         <v/>
       </c>
       <c r="D35" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" s="346"/>
       <c r="G35" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H35" s="349"/>
       <c r="I35" s="353"/>
@@ -25651,14 +25648,14 @@
         <v/>
       </c>
       <c r="D36" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F36" s="346"/>
       <c r="G36" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H36" s="349"/>
       <c r="I36" s="353"/>
@@ -25681,14 +25678,14 @@
         <v/>
       </c>
       <c r="D37" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E37" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F37" s="346"/>
       <c r="G37" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H37" s="349"/>
       <c r="I37" s="353"/>
@@ -25711,14 +25708,14 @@
         <v/>
       </c>
       <c r="D38" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F38" s="346"/>
       <c r="G38" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H38" s="349"/>
       <c r="I38" s="353"/>
@@ -25741,14 +25738,14 @@
         <v/>
       </c>
       <c r="D39" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E39" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F39" s="346"/>
       <c r="G39" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H39" s="349"/>
       <c r="I39" s="353"/>
@@ -25771,14 +25768,14 @@
         <v/>
       </c>
       <c r="D40" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F40" s="346"/>
       <c r="G40" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H40" s="349"/>
       <c r="I40" s="353"/>
@@ -25801,14 +25798,14 @@
         <v/>
       </c>
       <c r="D41" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F41" s="346"/>
       <c r="G41" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H41" s="349"/>
       <c r="I41" s="353"/>
@@ -25831,14 +25828,14 @@
         <v/>
       </c>
       <c r="D42" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F42" s="346"/>
       <c r="G42" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H42" s="349"/>
       <c r="I42" s="353"/>
@@ -25861,14 +25858,14 @@
         <v/>
       </c>
       <c r="D43" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F43" s="346"/>
       <c r="G43" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H43" s="349"/>
       <c r="I43" s="353"/>
@@ -25891,14 +25888,14 @@
         <v/>
       </c>
       <c r="D44" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F44" s="346"/>
       <c r="G44" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H44" s="349"/>
       <c r="I44" s="353"/>
@@ -25921,14 +25918,14 @@
         <v/>
       </c>
       <c r="D45" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E45" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F45" s="346"/>
       <c r="G45" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H45" s="349"/>
       <c r="I45" s="353"/>
@@ -25951,14 +25948,14 @@
         <v/>
       </c>
       <c r="D46" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F46" s="346"/>
       <c r="G46" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H46" s="349"/>
       <c r="I46" s="353"/>
@@ -25981,14 +25978,14 @@
         <v/>
       </c>
       <c r="D47" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F47" s="346"/>
       <c r="G47" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H47" s="349"/>
       <c r="I47" s="353"/>
@@ -26011,14 +26008,14 @@
         <v/>
       </c>
       <c r="D48" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E48" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F48" s="346"/>
       <c r="G48" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H48" s="349"/>
       <c r="I48" s="353"/>
@@ -26041,14 +26038,14 @@
         <v/>
       </c>
       <c r="D49" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F49" s="346"/>
       <c r="G49" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H49" s="349"/>
       <c r="I49" s="353"/>
@@ -26071,14 +26068,14 @@
         <v/>
       </c>
       <c r="D50" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F50" s="346"/>
       <c r="G50" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H50" s="349"/>
       <c r="I50" s="353"/>
@@ -26101,14 +26098,14 @@
         <v/>
       </c>
       <c r="D51" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E51" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F51" s="346"/>
       <c r="G51" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H51" s="349"/>
       <c r="I51" s="353"/>
@@ -26131,14 +26128,14 @@
         <v/>
       </c>
       <c r="D52" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F52" s="346"/>
       <c r="G52" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H52" s="349"/>
       <c r="I52" s="353"/>
@@ -26161,14 +26158,14 @@
         <v/>
       </c>
       <c r="D53" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E53" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F53" s="346"/>
       <c r="G53" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H53" s="349"/>
       <c r="I53" s="353"/>
@@ -26191,14 +26188,14 @@
         <v/>
       </c>
       <c r="D54" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F54" s="346"/>
       <c r="G54" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H54" s="349"/>
       <c r="I54" s="353"/>
@@ -26221,14 +26218,14 @@
         <v/>
       </c>
       <c r="D55" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F55" s="346"/>
       <c r="G55" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H55" s="349"/>
       <c r="I55" s="353"/>
@@ -26251,14 +26248,14 @@
         <v/>
       </c>
       <c r="D56" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F56" s="346"/>
       <c r="G56" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H56" s="349"/>
       <c r="I56" s="353"/>
@@ -26281,14 +26278,14 @@
         <v/>
       </c>
       <c r="D57" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F57" s="346"/>
       <c r="G57" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H57" s="349"/>
       <c r="I57" s="353"/>
@@ -26311,14 +26308,14 @@
         <v/>
       </c>
       <c r="D58" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E58" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F58" s="346"/>
       <c r="G58" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H58" s="349"/>
       <c r="I58" s="353"/>
@@ -26341,14 +26338,14 @@
         <v/>
       </c>
       <c r="D59" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F59" s="346"/>
       <c r="G59" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H59" s="349"/>
       <c r="I59" s="353"/>
@@ -26371,14 +26368,14 @@
         <v/>
       </c>
       <c r="D60" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E60" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F60" s="346"/>
       <c r="G60" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H60" s="349"/>
       <c r="I60" s="353"/>
@@ -26401,14 +26398,14 @@
         <v/>
       </c>
       <c r="D61" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F61" s="346"/>
       <c r="G61" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H61" s="349"/>
       <c r="I61" s="353"/>
@@ -26431,14 +26428,14 @@
         <v/>
       </c>
       <c r="D62" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F62" s="346"/>
       <c r="G62" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H62" s="349"/>
       <c r="I62" s="353"/>
@@ -26461,14 +26458,14 @@
         <v/>
       </c>
       <c r="D63" s="163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F63" s="346"/>
       <c r="G63" s="347" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H63" s="349"/>
       <c r="I63" s="353"/>
@@ -26481,7 +26478,7 @@
     <row r="64" spans="1:14" ht="27" customHeight="1" thickBot="1"/>
     <row r="65" spans="1:14" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B65" s="248" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C65" s="249"/>
       <c r="D65" s="249"/>
@@ -26506,10 +26503,10 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="K66" s="293" t="s">
         <v>83</v>
-      </c>
-      <c r="K66" s="293" t="s">
-        <v>84</v>
       </c>
       <c r="L66" s="293"/>
       <c r="M66" s="293"/>
@@ -26672,7 +26669,7 @@
     </row>
     <row r="75" spans="1:14" s="37" customFormat="1" ht="21.4" thickBot="1">
       <c r="B75" s="248" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C75" s="249"/>
       <c r="D75" s="249"/>
@@ -26715,7 +26712,7 @@
       <c r="H77" s="242"/>
       <c r="I77" s="242"/>
       <c r="J77" s="251" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K77" s="252"/>
       <c r="L77" s="252"/>
@@ -26832,7 +26829,7 @@
     </row>
     <row r="84" spans="1:14" ht="50.25" customHeight="1">
       <c r="B84" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C84" s="243"/>
       <c r="D84" s="243"/>
